--- a/giro_da_praça_ofertas - BLACK - JARDEL.xlsx
+++ b/giro_da_praça_ofertas - BLACK - JARDEL.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C297C9E-67B9-4100-871A-4AAE957B94CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34DDEC7-951F-468C-B711-D3D507BE791C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="324">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -121,12 +121,6 @@
     <t>PAPEL TOALHA SCALA 200 FOLHAS MULTIUSO</t>
   </si>
   <si>
-    <t>#08 BAZAR - COPOS</t>
-  </si>
-  <si>
-    <t>COPO DOSE NADIR OLÉ 60ML</t>
-  </si>
-  <si>
     <t>#08 BAZAR - DESCARTÁVEIS</t>
   </si>
   <si>
@@ -148,6 +142,9 @@
     <t>#08 BAZAR - PANELAS E UTENSÍLIOS DE COZINHA</t>
   </si>
   <si>
+    <t>COPO DOSE NADIR OLÉ VIDRO 60ML</t>
+  </si>
+  <si>
     <t>CUSCUZEIRO FOME ZERO ALILAR</t>
   </si>
   <si>
@@ -187,6 +184,9 @@
     <t>ESMALTE RISQUE 7,5ML</t>
   </si>
   <si>
+    <t>DIAMOND GEL TOP COAT FIXADOR, GUERREIRA DO ARCO IRIS</t>
+  </si>
+  <si>
     <t>ESMALTE RISQUE 8ML</t>
   </si>
   <si>
@@ -226,6 +226,9 @@
     <t>FLOCÃO DE MILHO BONOMILHO 500G</t>
   </si>
   <si>
+    <t>MASSA PARA TAPIOCA AMAFIL 1KG</t>
+  </si>
+  <si>
     <t>POLVILHO MATUTO 1KG AZEDO</t>
   </si>
   <si>
@@ -274,7 +277,16 @@
     <t>DOCE DE PESSEGO GB 450G METADES</t>
   </si>
   <si>
-    <t>FARINHA LACTEA NESTLE 160G ORIGINAL</t>
+    <t>FARINHA LACTEA NESTLÉ 160G ORIGINAL</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
+  </si>
+  <si>
+    <t>TODDYNHO 200ML</t>
+  </si>
+  <si>
+    <t>CHOCOLATE</t>
   </si>
   <si>
     <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
@@ -295,10 +307,10 @@
     <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
   </si>
   <si>
-    <t xml:space="preserve">LEITE ITALAC 1L INTEGRAL ZERO LACTOSE </t>
-  </si>
-  <si>
-    <t>LEITE LEITBOM 1L INTEGRAL</t>
+    <t xml:space="preserve">LEITE LONGA VIDA ITALAC 1L INTEGRAL ZERO LACTOSE </t>
+  </si>
+  <si>
+    <t>LEITE LONGA VIDA LEITBOM 1L INTEGRAL</t>
   </si>
   <si>
     <t>#02 MERCEARIA - LATICÍNIOS - LEITE EM PÓ</t>
@@ -328,12 +340,15 @@
     <t xml:space="preserve">AZEITONAS VERDES RIVOLI DOYPACK 200G </t>
   </si>
   <si>
-    <t>COGUMELO OLE 160G INTEIRO</t>
+    <t>COGUMELO OLÉ 160G INTEIRO</t>
   </si>
   <si>
     <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
   </si>
   <si>
+    <t>EXTRATO DE TOMATE OLE COPO 190G</t>
+  </si>
+  <si>
     <t>KETCHUP QUERO 400G</t>
   </si>
   <si>
@@ -349,13 +364,16 @@
     <t>MOLHO DE TOMATE SÓ FRUTA 300G TRADICIONAL</t>
   </si>
   <si>
+    <t>MOLHO QUERO PRONTO SACHÊ 240G TRADICIONAL</t>
+  </si>
+  <si>
     <t>TEMPERO COMPLETO ARISCO 1KG COM PIMENTA</t>
   </si>
   <si>
     <t>TEMPERO COMPLETO SABORELLE 270G</t>
   </si>
   <si>
-    <t>TEMPERO SABORELLE 270G SEM PIMENTA</t>
+    <t>SEM PIMENTA, TRADICIONAL</t>
   </si>
   <si>
     <t>VINAGRE CASTELO 750ML</t>
@@ -367,6 +385,9 @@
     <t>#02 MERCEARIA - CONSERVAS - HORTIFRUTI</t>
   </si>
   <si>
+    <t>MILHO VERDE QUERO LATA 170G</t>
+  </si>
+  <si>
     <t>MILHO VERDE SOFRUTA LATA 170G</t>
   </si>
   <si>
@@ -571,10 +592,10 @@
     <t>#03 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
   </si>
   <si>
-    <t>AGUA SANITÁRIA QBOA 1L</t>
-  </si>
-  <si>
-    <t>AGUA SANITÁRIA QBOA 2L</t>
+    <t>ÁGUA SANITÁRIA QBOA 1L</t>
+  </si>
+  <si>
+    <t>ÁGUA SANITÁRIA QBOA 2L</t>
   </si>
   <si>
     <t>#03 LIMPEZA - AMACIANTES</t>
@@ -649,21 +670,21 @@
     <t>SABÃO EM BARRA YPÊ 900G NEUTRO</t>
   </si>
   <si>
+    <t>SABÃO EM PÓ BRILHANTE CAIXA 1,6KG LIMPEZA TOTAL</t>
+  </si>
+  <si>
     <t>SABÃO EM PÓ BRILHANTE SACHÊ 1,6KG LIMPEZA TOTAL</t>
   </si>
   <si>
     <t>SABÃO EM PÓ OMO CAIXA 800G LAVAGEM PERFEITA</t>
   </si>
   <si>
-    <t>SABÃO EM PÓ TIXAN YPE CAIXA 400G</t>
+    <t>SABÃO EM PÓ TIXAN YPÊ CAIXA 800G</t>
   </si>
   <si>
     <t>MACIEZ, PRIMAVERA</t>
   </si>
   <si>
-    <t>SABÃO EM PÓ TIXAN YPÊ CAIXA 800G</t>
-  </si>
-  <si>
     <t>SABÃO LIQUIDO OMO 3L MULTIACAO</t>
   </si>
   <si>
@@ -736,21 +757,12 @@
     <t>MARGARINA DELICIA 1KG COM CREME DE LEITE</t>
   </si>
   <si>
-    <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
-  </si>
-  <si>
     <t>IOGURTE DANONE 1250G</t>
   </si>
   <si>
     <t>COCO, MORANGO, VITAMINA DE FRUTAS</t>
   </si>
   <si>
-    <t>TODDYNHO 200ML</t>
-  </si>
-  <si>
-    <t>CHOCOLATE</t>
-  </si>
-  <si>
     <t>REQUEIJÃO BOUA 180G CREMOSO TRADICIONAL</t>
   </si>
   <si>
@@ -808,31 +820,22 @@
     <t>CREME PARA PENTEAR TURMA DA XUXINHA BARUEL 150ML CACHOS</t>
   </si>
   <si>
-    <t>KIT SHAMPOO + CONDICIONADOR TURMA DA XUXINHA BARUEL 400ML / 210ML</t>
-  </si>
-  <si>
-    <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD 275ML / 175ML SALVA FIOS</t>
-  </si>
-  <si>
-    <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD 285ML / 175ML DETOX</t>
-  </si>
-  <si>
-    <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD 300ML</t>
-  </si>
-  <si>
-    <t>200ML HIDRATANTE AGUA COCO, 200ML QUERATINA REPARAÇÃO, 500ML LISO PROLONGADADO, ÓLEO DE ARGAN</t>
-  </si>
-  <si>
-    <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD 450ML DEFESA PROLONGADA</t>
-  </si>
-  <si>
-    <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD 500ML / 200ML COMPRIDOS E FORTES</t>
-  </si>
-  <si>
-    <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD 500ML NUTRIÇÃO PODER 500ML</t>
-  </si>
-  <si>
-    <t>SHAMPOO + CONDICIONADOR TURMA DA XUXINHA BARUEL 400ML + 210ML</t>
+    <t>KIT SHAMPOO + CONDICIONADOR TURMA DA XUXINHA BARUEL</t>
+  </si>
+  <si>
+    <t>KIT SHAMPOO + CONDICIONADOR TURMA DA XUXINHA BARUEL INFANTIL</t>
+  </si>
+  <si>
+    <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD 1KIT</t>
+  </si>
+  <si>
+    <t>COMPRIDOS E FORTES, DEFESA PROLONGADA, HIDRATANTE ÁGUA COCO, LISO PROLONGADADO, QUERATINA REPARAÇÃO, SALVA FIOS, ÓLEO DE ARGAN</t>
+  </si>
+  <si>
+    <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD 1KIT DETOX</t>
+  </si>
+  <si>
+    <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD 1KIT NUTRIÇÃO PODER</t>
   </si>
   <si>
     <t>SHAMPOO TURMA DA XUXINHA BARUEL 120ML</t>
@@ -844,9 +847,6 @@
     <t>TINTURA CAPILAR BIOCOLOR MINI KIT 1UN</t>
   </si>
   <si>
-    <t>1.0 PRETO, 10.0 LOURO ULTRA CLARO, 12.11 LOURISSIMO, 2.0 PRETO AZULADO, 3.0 CASTANHO ESCURO CHIQUE, 30ML PRETO INTENSO, 4.0 CASTANHO MALICIA, 4.5 ACAJU ESCURO, 5.0 CASTANHO, 5.1 CASTANHO FESTA, 5.3 CASTANHA CLARO DOURADO, 5.59 ACAJU PURPURA, 6.0 LOURO ESCURO, 6.1 LOURO CINZA ESCURO, 6.66 VERMELHO INTENSO, 6.7 CHOCOLATE, 7.0 LOURO ARRASO, 7.1 LORO CINZA MÉDIO, 7.3 LOURO DOURADO, 7.44 COBRE INTENSO, 8.0 LOURO CLARO RADIANTE, 8.1 LOURO ACINZENTADO ESTILOSO</t>
-  </si>
-  <si>
     <t>#04 HIGIENE PESSOAL - DESODORANTE</t>
   </si>
   <si>
@@ -862,16 +862,22 @@
     <t>BIO PROTECT, SENSITIVE, VANILLA</t>
   </si>
   <si>
+    <t>DESODORANTE MOOD AEROSOL 150ML</t>
+  </si>
+  <si>
     <t>#04 HIGIENE PESSOAL - FRALDAS</t>
   </si>
   <si>
-    <t>FRALDA DESCARTAVEL POM POM 1PCT</t>
-  </si>
-  <si>
-    <t>12UN SHORTINHO JUMBINHO XXG, 16UN SHORTINHO JUMBINHO G, 18UN SHORTINHO JUMBINHO M</t>
-  </si>
-  <si>
-    <t>24UN SHORTINHO JUMBO XXG, 34UN SHORTINHO JUMBO M</t>
+    <t>FRALDA DESCARTAVEL POM POM SHORTINHO JUMBINHO 1PCT</t>
+  </si>
+  <si>
+    <t>12UN XXG, 16UN G, 18UN M</t>
+  </si>
+  <si>
+    <t>FRALDA DESCARTAVEL POM POM SHORTINHO JUMBO 1PCT</t>
+  </si>
+  <si>
+    <t>24UN XXG, 34UN M</t>
   </si>
   <si>
     <t>#04 HIGIENE PESSOAL - HIGIENE BUCAL</t>
@@ -889,10 +895,10 @@
     <t>ABSORVENTE INTIMUS 16UN 1PCT NOTURNO COM ABAS SUAVE</t>
   </si>
   <si>
-    <t>ABSORVENTE INTIMUS GEL 8 X 1UN</t>
-  </si>
-  <si>
-    <t>1PCT NOTURNO SECA COM ABAS, 1PCT NOTURNO SUAVE COM ABAS</t>
+    <t>ABSORVENTE INTIMUS GEL 8 X 1 1PCT</t>
+  </si>
+  <si>
+    <t>NOTURNO SECA COM ABAS, NOTURNO SUAVE COM ABAS</t>
   </si>
   <si>
     <t>HASTES FLEXIVEIS COTTONBABY POTE 150UN</t>
@@ -907,6 +913,24 @@
     <t>LENÇOS UMEDECIDOS COTTONBABY 50UN RECEM NASCIDO</t>
   </si>
   <si>
+    <t>#04 HIGIENE PESSOAL - MASCULINO</t>
+  </si>
+  <si>
+    <t>CREME DE BARBEAR BOZZANO 65G</t>
+  </si>
+  <si>
+    <t>ALOE VERA, MENTOLADO, PELE SENSIVEL</t>
+  </si>
+  <si>
+    <t>#04 HIGIENE PESSOAL - PAPEL HIGIENICO</t>
+  </si>
+  <si>
+    <t>PAPEL HIGIENICO MIMMO 16 X 30M PROMOCIONAL</t>
+  </si>
+  <si>
+    <t>PAPEL HIGIÊNICO NEVE 4 X 30M NEUTRO</t>
+  </si>
+  <si>
     <t>#04 HIGIENE PESSOAL - SABONETE</t>
   </si>
   <si>
@@ -949,13 +973,7 @@
     <t>AMACIANTE DE ROUPAS TUFF 1L</t>
   </si>
   <si>
-    <t>CONCENTRADO LE JARDIM, CONCENTRADO POEME, CONCENTRADO ROSE PINK, CONCENTRADO SPLENDOR</t>
-  </si>
-  <si>
     <t>DESINFETANTE AZULIM START 1L</t>
-  </si>
-  <si>
-    <t>ABSOLUTE, ERVA DOCE, FLORATA, LAVANDA, MARINER, NEON, VIOLETTE, WAVE</t>
   </si>
   <si>
     <t>DESINFETANTE START VOREL 2L</t>
@@ -981,7 +999,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -995,24 +1013,6 @@
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="7"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1035,6 +1035,24 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1085,46 +1103,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1431,15 +1453,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F219"/>
-  <sheetFormatPr defaultColWidth="35.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F223"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="64.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.85546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.28515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1455,10 +1477,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1475,25 +1497,25 @@
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="5">
+      <c r="E2" s="13"/>
+      <c r="F2" s="9">
         <v>20.49</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="3">
         <v>325990</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="12"/>
+      <c r="E3" s="13"/>
       <c r="F3" s="9">
         <v>17.989999999999998</v>
       </c>
@@ -1511,8 +1533,8 @@
       <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="5">
+      <c r="E4" s="13"/>
+      <c r="F4" s="9">
         <v>14.99</v>
       </c>
     </row>
@@ -1529,43 +1551,43 @@
       <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="5">
+      <c r="E5" s="13"/>
+      <c r="F5" s="9">
         <v>20.99</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="3">
         <v>100020</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="12"/>
+      <c r="E6" s="13"/>
       <c r="F6" s="9">
         <v>19.989999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="3">
         <v>100031</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="12"/>
+      <c r="E7" s="13"/>
       <c r="F7" s="9">
         <v>22.99</v>
       </c>
@@ -1583,8 +1605,8 @@
       <c r="D8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="5">
+      <c r="E8" s="13"/>
+      <c r="F8" s="9">
         <v>6.99</v>
       </c>
     </row>
@@ -1601,8 +1623,8 @@
       <c r="D9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="5">
+      <c r="E9" s="13"/>
+      <c r="F9" s="9">
         <v>6.99</v>
       </c>
     </row>
@@ -1619,8 +1641,8 @@
       <c r="D10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="5">
+      <c r="E10" s="13"/>
+      <c r="F10" s="9">
         <v>5.49</v>
       </c>
     </row>
@@ -1637,8 +1659,8 @@
       <c r="D11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="5">
+      <c r="E11" s="13"/>
+      <c r="F11" s="9">
         <v>5.99</v>
       </c>
     </row>
@@ -1655,8 +1677,8 @@
       <c r="D12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="5">
+      <c r="E12" s="13"/>
+      <c r="F12" s="9">
         <v>4.99</v>
       </c>
     </row>
@@ -1673,43 +1695,43 @@
       <c r="D13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="5">
+      <c r="E13" s="13"/>
+      <c r="F13" s="9">
         <v>6.99</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="3">
         <v>106680</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="12"/>
+      <c r="E14" s="13"/>
       <c r="F14" s="9">
         <v>7.99</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="48" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="3">
         <v>311070</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="13" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="9">
@@ -1717,3398 +1739,3474 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="3">
         <v>318660</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="12"/>
+      <c r="E17" s="13"/>
       <c r="F17" s="9">
         <v>24.99</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="3">
         <v>102294</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="12"/>
+      <c r="E19" s="13"/>
       <c r="F19" s="9">
         <v>5.99</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="3">
         <v>312887</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="12"/>
+      <c r="E20" s="13"/>
       <c r="F20" s="9">
         <v>5.99</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="7">
-        <v>113856</v>
-      </c>
-      <c r="D22" s="8" t="s">
+      <c r="C22" s="3">
+        <v>189135</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="12"/>
+      <c r="E22" s="13"/>
       <c r="F22" s="9">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="7">
-        <v>189135</v>
-      </c>
-      <c r="D23" s="8" t="s">
+      <c r="C23" s="3">
+        <v>102416</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="12"/>
+      <c r="E23" s="13"/>
       <c r="F23" s="9">
         <v>5.99</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="3">
+        <v>302449</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="7">
-        <v>102416</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="12"/>
+      <c r="E24" s="13"/>
       <c r="F24" s="9">
         <v>5.99</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="7">
-        <v>302449</v>
-      </c>
-      <c r="D25" s="8" t="s">
+      <c r="B25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="3">
+        <v>311244</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="13"/>
+      <c r="F25" s="9">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="9">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="7">
-        <v>311244</v>
-      </c>
-      <c r="D26" s="8" t="s">
+      <c r="C26" s="3">
+        <v>113856</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="12"/>
+      <c r="E26" s="13"/>
       <c r="F26" s="9">
         <v>4.99</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="3">
+        <v>199260</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="7">
-        <v>199260</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="12"/>
+      <c r="E27" s="13"/>
       <c r="F27" s="9">
         <v>49.99</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="7">
+      <c r="B28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="3">
         <v>239161</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" s="12"/>
+      <c r="D28" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="13"/>
       <c r="F28" s="9">
         <v>45.99</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="3">
+        <v>134383</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="7">
-        <v>134383</v>
-      </c>
-      <c r="D29" s="8" t="s">
+      <c r="E29" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>46</v>
       </c>
       <c r="F29" s="9">
         <v>29.99</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="7">
+      <c r="B30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="3">
         <v>214439</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="13" t="s">
         <v>47</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>48</v>
       </c>
       <c r="F30" s="9">
         <v>45.99</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="C32" s="3">
+        <v>111807</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="7">
-        <v>111807</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" s="12"/>
+      <c r="E32" s="13"/>
       <c r="F32" s="9">
         <v>21.99</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+    <row r="34" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="C34" s="3">
+        <v>271863</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="7">
-        <v>271863</v>
-      </c>
-      <c r="D34" s="8" t="s">
+      <c r="E34" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="12"/>
       <c r="F34" s="9">
         <v>5.49</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="7">
+      <c r="C35" s="3">
         <v>308384</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E35" s="12"/>
+      <c r="E35" s="13"/>
       <c r="F35" s="9">
         <v>5.49</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="3">
         <v>100061</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E37" s="12"/>
+      <c r="E37" s="13"/>
       <c r="F37" s="9">
         <v>4.99</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="3">
         <v>112978</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="12"/>
+      <c r="E38" s="13"/>
       <c r="F38" s="9">
         <v>2.89</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="3">
         <v>128930</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E39" s="12"/>
+      <c r="E39" s="13"/>
       <c r="F39" s="9">
         <v>6.39</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="3">
         <v>107361</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E40" s="12"/>
+      <c r="E40" s="13"/>
       <c r="F40" s="9">
         <v>5.89</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="3">
         <v>100024</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E41" s="12"/>
+      <c r="E41" s="13"/>
       <c r="F41" s="9">
         <v>5.69</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="3">
         <v>100027</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E42" s="12"/>
+      <c r="E42" s="13"/>
       <c r="F42" s="9">
         <v>7.99</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="3">
         <v>294705</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E43" s="12"/>
+      <c r="E43" s="13"/>
       <c r="F43" s="9">
         <v>2.39</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="3">
         <v>255841</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E44" s="12"/>
+      <c r="E44" s="13"/>
       <c r="F44" s="9">
         <v>2.89</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="3">
         <v>100120</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="12"/>
+      <c r="E45" s="13"/>
       <c r="F45" s="9">
         <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C46" s="6">
+        <v>149122</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="15"/>
+      <c r="F46" s="11">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47" s="3">
         <v>145874</v>
       </c>
-      <c r="D46" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E46" s="12"/>
-      <c r="F46" s="9">
+      <c r="D47" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="13"/>
+      <c r="F47" s="9">
         <v>10.49</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B48" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C48" s="3">
         <v>128920</v>
       </c>
-      <c r="D47" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E47" s="12"/>
-      <c r="F47" s="9">
+      <c r="D48" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" s="13"/>
+      <c r="F48" s="9">
         <v>6.99</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B49" s="6" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C49" s="7">
+      <c r="B50" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" s="3">
         <v>255232</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D50" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E50" s="13"/>
+      <c r="F50" s="9">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E49" s="12"/>
-      <c r="F49" s="9">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B50" s="6" t="s">
+      <c r="C51" s="3">
+        <v>101137</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E51" s="13"/>
+      <c r="F51" s="9">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C50" s="7">
-        <v>101137</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E50" s="12"/>
-      <c r="F50" s="9">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B51" s="6" t="s">
+      <c r="B52" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C51" s="7">
+      <c r="C52" s="3">
         <v>261728</v>
       </c>
-      <c r="D51" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E51" s="12"/>
-      <c r="F51" s="9">
+      <c r="D52" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E52" s="13"/>
+      <c r="F52" s="9">
         <v>6.99</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B52" s="6" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C52" s="7">
+      <c r="C53" s="3">
         <v>186826</v>
       </c>
-      <c r="D52" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E52" s="12"/>
-      <c r="F52" s="9">
+      <c r="D53" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E53" s="13"/>
+      <c r="F53" s="9">
         <v>5.39</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B53" s="6" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C53" s="7">
+      <c r="C54" s="3">
         <v>250013</v>
       </c>
-      <c r="D53" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E53" s="12"/>
-      <c r="F53" s="9">
+      <c r="D54" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B54" s="6" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C54" s="7">
+      <c r="C55" s="3">
         <v>286197</v>
       </c>
-      <c r="D54" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E54" s="12"/>
-      <c r="F54" s="9">
+      <c r="D55" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E55" s="13"/>
+      <c r="F55" s="9">
         <v>8.59</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="36" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C55" s="3">
+    <row r="56" spans="1:6" ht="36" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56" s="3">
         <v>297920</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D56" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F56" s="9">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E55" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="F55" s="5">
-        <v>6.59</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C56" s="7">
+      <c r="C57" s="3">
         <v>202443</v>
       </c>
-      <c r="D56" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E56" s="12"/>
-      <c r="F56" s="9">
+      <c r="D57" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E57" s="13"/>
+      <c r="F57" s="9">
         <v>11.99</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C57" s="7">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C58" s="3">
         <v>114256</v>
       </c>
-      <c r="D57" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E57" s="12"/>
-      <c r="F57" s="9">
+      <c r="D58" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E58" s="13"/>
+      <c r="F58" s="9">
         <v>17.989999999999998</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" s="7">
-        <v>273006</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E58" s="12"/>
-      <c r="F58" s="9">
-        <v>6.99</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C59" s="3">
+        <v>273006</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C59" s="3">
+      <c r="E59" s="13"/>
+      <c r="F59" s="9">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C60" s="3">
+        <v>101874</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F60" s="9">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C61" s="3">
         <v>101066</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E59" s="11"/>
-      <c r="F59" s="5">
+      <c r="D61" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E61" s="13"/>
+      <c r="F61" s="9">
         <v>3.29</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C60" s="7">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C62" s="3">
         <v>155079</v>
       </c>
-      <c r="D60" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E60" s="12"/>
-      <c r="F60" s="9">
+      <c r="D62" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E62" s="13"/>
+      <c r="F62" s="9">
         <v>3.49</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C61" s="7">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C63" s="3">
         <v>108434</v>
       </c>
-      <c r="D61" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E61" s="12"/>
-      <c r="F61" s="9">
+      <c r="D63" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E63" s="13"/>
+      <c r="F63" s="9">
         <v>6.99</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C62" s="7">
-        <v>101083</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E62" s="12"/>
-      <c r="F62" s="9">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C63" s="7">
-        <v>219003</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E63" s="12"/>
-      <c r="F63" s="9">
-        <v>7.59</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C64" s="3">
+        <v>101083</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E64" s="13"/>
+      <c r="F64" s="9">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C65" s="3">
+        <v>219003</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E65" s="13"/>
+      <c r="F65" s="9">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C66" s="3">
         <v>170363</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E64" s="11"/>
-      <c r="F64" s="5">
+      <c r="D66" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E66" s="13"/>
+      <c r="F66" s="9">
         <v>6.19</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C65" s="7">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C67" s="3">
         <v>106922</v>
       </c>
-      <c r="D65" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E65" s="12"/>
-      <c r="F65" s="9">
+      <c r="D67" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E67" s="13"/>
+      <c r="F67" s="9">
         <v>41.99</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C66" s="7">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C68" s="3">
         <v>307145</v>
       </c>
-      <c r="D66" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E66" s="12"/>
-      <c r="F66" s="9">
+      <c r="D68" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E68" s="13"/>
+      <c r="F68" s="9">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C68" s="7">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C70" s="3">
         <v>132657</v>
       </c>
-      <c r="D68" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E68" s="12"/>
-      <c r="F68" s="9">
+      <c r="D70" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E70" s="13"/>
+      <c r="F70" s="9">
         <v>47.99</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C69" s="7">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C71" s="3">
         <v>100709</v>
       </c>
-      <c r="D69" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E69" s="12"/>
-      <c r="F69" s="9">
+      <c r="D71" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E71" s="13"/>
+      <c r="F71" s="9">
         <v>35.99</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C70" s="7">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C72" s="3">
         <v>100737</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="D72" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E72" s="13"/>
+      <c r="F72" s="9">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E70" s="12"/>
-      <c r="F70" s="9">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C71" s="7">
+      <c r="B73" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C73" s="3">
         <v>289034</v>
       </c>
-      <c r="D71" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="E71" s="12"/>
-      <c r="F71" s="9">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C72" s="7">
-        <v>312579</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E72" s="12"/>
-      <c r="F72" s="9">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C73" s="7">
-        <v>273714</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E73" s="12"/>
+      <c r="D73" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E73" s="13"/>
       <c r="F73" s="9">
         <v>7.99</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C74" s="7">
+      <c r="A74" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C74" s="3">
+        <v>312579</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E74" s="13"/>
+      <c r="F74" s="9">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C75" s="3">
+        <v>273714</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E75" s="13"/>
+      <c r="F75" s="9">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C76" s="6">
+        <v>100780</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E76" s="15"/>
+      <c r="F76" s="11">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C77" s="3">
         <v>100789</v>
       </c>
-      <c r="D74" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="F74" s="9">
+      <c r="D77" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="F77" s="9">
         <v>8.49</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C75" s="7">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C78" s="3">
         <v>101728</v>
       </c>
-      <c r="D75" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E75" s="12"/>
-      <c r="F75" s="9">
+      <c r="D78" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E78" s="13"/>
+      <c r="F78" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C76" s="7">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C79" s="3">
         <v>115724</v>
       </c>
-      <c r="D76" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E76" s="12"/>
-      <c r="F76" s="9">
+      <c r="D79" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E79" s="13"/>
+      <c r="F79" s="9">
         <v>2.89</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C77" s="7">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C80" s="3">
         <v>259414</v>
       </c>
-      <c r="D77" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E77" s="12"/>
-      <c r="F77" s="9">
+      <c r="D80" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E80" s="13"/>
+      <c r="F80" s="9">
         <v>2.19</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C78" s="7">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C81" s="6">
+        <v>321107</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E81" s="15"/>
+      <c r="F81" s="11">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C82" s="3">
         <v>100876</v>
       </c>
-      <c r="D78" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E78" s="12"/>
-      <c r="F78" s="9">
+      <c r="D82" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E82" s="13"/>
+      <c r="F82" s="9">
         <v>14.49</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C79" s="7">
-        <v>108528</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E79" s="12"/>
-      <c r="F79" s="9">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C83" s="3">
+        <v>119560</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F83" s="9">
         <v>5.49</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C80" s="7">
-        <v>119560</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="E80" s="12"/>
-      <c r="F80" s="9">
-        <v>5.49</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C81" s="7">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C84" s="3">
         <v>106961</v>
       </c>
-      <c r="D81" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E81" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F81" s="9">
+      <c r="D84" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F84" s="9">
         <v>3.89</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C82" s="7">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C85" s="6">
+        <v>107640</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E85" s="15"/>
+      <c r="F85" s="11">
+        <v>4.1900000000000004</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C86" s="3">
         <v>234316</v>
       </c>
-      <c r="D82" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="E82" s="12"/>
-      <c r="F82" s="9">
+      <c r="D86" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E86" s="13"/>
+      <c r="F86" s="9">
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C83" s="7">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C87" s="3">
         <v>100754</v>
       </c>
-      <c r="D83" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E83" s="12"/>
-      <c r="F83" s="9">
+      <c r="D87" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E87" s="13"/>
+      <c r="F87" s="9">
         <v>23.99</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C84" s="7">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C88" s="3">
         <v>287208</v>
       </c>
-      <c r="D84" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="E84" s="12"/>
-      <c r="F84" s="9">
+      <c r="D88" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E88" s="13"/>
+      <c r="F88" s="9">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C85" s="7">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C89" s="3">
         <v>100705</v>
       </c>
-      <c r="D85" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E85" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="F85" s="9">
+      <c r="D89" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="F89" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C86" s="7">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C90" s="3">
         <v>142475</v>
       </c>
-      <c r="D86" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E86" s="12"/>
-      <c r="F86" s="9">
+      <c r="D90" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E90" s="13"/>
+      <c r="F90" s="9">
         <v>3.19</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C87" s="7">
-        <v>100642</v>
-      </c>
-      <c r="D87" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E87" s="12"/>
-      <c r="F87" s="9">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C88" s="7">
-        <v>274807</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="E88" s="12"/>
-      <c r="F88" s="9">
-        <v>2.89</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C89" s="7">
-        <v>100632</v>
-      </c>
-      <c r="D89" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E89" s="12"/>
-      <c r="F89" s="9">
-        <v>11.99</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C91" s="3">
-        <v>108686</v>
+        <v>100642</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E91" s="11"/>
-      <c r="F91" s="5">
-        <v>7.69</v>
+        <v>130</v>
+      </c>
+      <c r="E91" s="13"/>
+      <c r="F91" s="9">
+        <v>2.99</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C92" s="3">
-        <v>104406</v>
+        <v>274807</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E92" s="11"/>
-      <c r="F92" s="5">
-        <v>11.49</v>
+        <v>131</v>
+      </c>
+      <c r="E92" s="13"/>
+      <c r="F92" s="9">
+        <v>2.89</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C93" s="3">
-        <v>104404</v>
+        <v>100632</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E93" s="11"/>
-      <c r="F93" s="5">
-        <v>10.49</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C94" s="3">
-        <v>104403</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E94" s="11"/>
-      <c r="F94" s="5">
-        <v>10.19</v>
+        <v>132</v>
+      </c>
+      <c r="E93" s="13"/>
+      <c r="F93" s="9">
+        <v>11.99</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C95" s="3">
-        <v>104410</v>
+        <v>108686</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E95" s="11"/>
-      <c r="F95" s="5">
-        <v>9.49</v>
+        <v>135</v>
+      </c>
+      <c r="E95" s="13"/>
+      <c r="F95" s="9">
+        <v>7.69</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C96" s="3">
-        <v>102287</v>
+        <v>104406</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E96" s="11"/>
-      <c r="F96" s="5">
-        <v>4.3899999999999997</v>
+        <v>136</v>
+      </c>
+      <c r="E96" s="13"/>
+      <c r="F96" s="9">
+        <v>11.49</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C97" s="3">
-        <v>117100</v>
+        <v>104404</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E97" s="11"/>
-      <c r="F97" s="5">
-        <v>12.99</v>
+        <v>137</v>
+      </c>
+      <c r="E97" s="13"/>
+      <c r="F97" s="9">
+        <v>10.49</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C98" s="3">
-        <v>286325</v>
+        <v>104403</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E98" s="11"/>
-      <c r="F98" s="5">
-        <v>22.99</v>
+        <v>138</v>
+      </c>
+      <c r="E98" s="13"/>
+      <c r="F98" s="9">
+        <v>10.19</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C99" s="3">
-        <v>264452</v>
+        <v>104410</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E99" s="11"/>
-      <c r="F99" s="5">
-        <v>5.99</v>
+        <v>139</v>
+      </c>
+      <c r="E99" s="13"/>
+      <c r="F99" s="9">
+        <v>9.49</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C100" s="3">
-        <v>247800</v>
+        <v>102287</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E100" s="11"/>
-      <c r="F100" s="5">
-        <v>6.29</v>
+        <v>141</v>
+      </c>
+      <c r="E100" s="13"/>
+      <c r="F100" s="9">
+        <v>4.3899999999999997</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C101" s="3">
-        <v>247799</v>
+        <v>117100</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E101" s="11"/>
-      <c r="F101" s="5">
-        <v>6.29</v>
+        <v>142</v>
+      </c>
+      <c r="E101" s="13"/>
+      <c r="F101" s="9">
+        <v>12.99</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C102" s="3">
-        <v>242930</v>
+        <v>286325</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="E102" s="11"/>
-      <c r="F102" s="5">
-        <v>7.19</v>
+        <v>144</v>
+      </c>
+      <c r="E102" s="13"/>
+      <c r="F102" s="9">
+        <v>22.99</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C103" s="3">
-        <v>239446</v>
+        <v>264452</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E103" s="11"/>
-      <c r="F103" s="5">
-        <v>3.19</v>
+        <v>145</v>
+      </c>
+      <c r="E103" s="13"/>
+      <c r="F103" s="9">
+        <v>5.99</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C104" s="3">
-        <v>168712</v>
+        <v>247800</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E104" s="11"/>
-      <c r="F104" s="5">
-        <v>3.39</v>
+        <v>147</v>
+      </c>
+      <c r="E104" s="13"/>
+      <c r="F104" s="9">
+        <v>6.29</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C105" s="3">
-        <v>170451</v>
+        <v>247799</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="E105" s="11"/>
-      <c r="F105" s="5">
-        <v>3.29</v>
+        <v>148</v>
+      </c>
+      <c r="E105" s="13"/>
+      <c r="F105" s="9">
+        <v>6.29</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C106" s="3">
-        <v>108423</v>
+        <v>242930</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E106" s="11"/>
-      <c r="F106" s="5">
+        <v>149</v>
+      </c>
+      <c r="E106" s="13"/>
+      <c r="F106" s="9">
         <v>7.19</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C107" s="3">
-        <v>265727</v>
+        <v>239446</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="E107" s="11"/>
-      <c r="F107" s="5">
-        <v>4.49</v>
+        <v>151</v>
+      </c>
+      <c r="E107" s="13"/>
+      <c r="F107" s="9">
+        <f>12*3.19</f>
+        <v>38.28</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C108" s="3">
-        <v>324556</v>
+        <v>168712</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="E108" s="11"/>
-      <c r="F108" s="5">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="E108" s="13"/>
+      <c r="F108" s="9">
+        <f>15*3.39</f>
+        <v>50.85</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C109" s="3">
-        <v>236674</v>
+        <v>170451</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E109" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="F109" s="5">
-        <v>42.99</v>
+        <v>153</v>
+      </c>
+      <c r="E109" s="13"/>
+      <c r="F109" s="9">
+        <f>15*3.29</f>
+        <v>49.35</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C110" s="3">
-        <v>293188</v>
+        <v>108423</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E110" s="11"/>
-      <c r="F110" s="5">
-        <v>7.19</v>
+        <v>154</v>
+      </c>
+      <c r="E110" s="13"/>
+      <c r="F110" s="9">
+        <f>6*7.19</f>
+        <v>43.14</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C111" s="3">
-        <v>102085</v>
+        <v>265727</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E111" s="11"/>
-      <c r="F111" s="5">
-        <v>13.49</v>
+        <v>155</v>
+      </c>
+      <c r="E111" s="13"/>
+      <c r="F111" s="9">
+        <f>8*4.49</f>
+        <v>35.92</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C112" s="3">
-        <v>215568</v>
+        <v>324556</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E112" s="11"/>
-      <c r="F112" s="5">
-        <v>39.99</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+      <c r="E112" s="13"/>
+      <c r="F112" s="9">
+        <f>15*3.09</f>
+        <v>46.349999999999994</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C113" s="3">
-        <v>301843</v>
+        <v>236674</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E113" s="11"/>
-      <c r="F113" s="5">
-        <v>74.989999999999995</v>
+        <v>158</v>
+      </c>
+      <c r="E113" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="F113" s="9">
+        <v>42.99</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C114" s="3">
-        <v>206930</v>
+        <v>293188</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E114" s="11"/>
-      <c r="F114" s="5">
-        <v>148.99</v>
+        <v>160</v>
+      </c>
+      <c r="E114" s="13"/>
+      <c r="F114" s="9">
+        <v>7.19</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C115" s="3">
-        <v>123548</v>
+        <v>102085</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E115" s="11"/>
-      <c r="F115" s="5">
-        <v>134.99</v>
+        <v>161</v>
+      </c>
+      <c r="E115" s="13"/>
+      <c r="F115" s="9">
+        <v>13.49</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C116" s="3">
-        <v>102077</v>
+        <v>215568</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E116" s="11"/>
-      <c r="F116" s="5">
-        <v>189.99</v>
+        <v>162</v>
+      </c>
+      <c r="E116" s="13"/>
+      <c r="F116" s="9">
+        <v>39.99</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C117" s="3">
-        <v>109729</v>
+        <v>301843</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E117" s="11"/>
-      <c r="F117" s="5">
-        <v>109.99</v>
+        <v>163</v>
+      </c>
+      <c r="E117" s="13"/>
+      <c r="F117" s="9">
+        <v>74.989999999999995</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C118" s="3">
-        <v>295198</v>
+        <v>206930</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="E118" s="11"/>
-      <c r="F118" s="5">
-        <v>11.69</v>
+        <v>164</v>
+      </c>
+      <c r="E118" s="13"/>
+      <c r="F118" s="9">
+        <v>148.99</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C119" s="3">
-        <v>102036</v>
+        <v>123548</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E119" s="11"/>
-      <c r="F119" s="5">
-        <v>24.99</v>
+        <v>165</v>
+      </c>
+      <c r="E119" s="13"/>
+      <c r="F119" s="9">
+        <v>134.99</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C120" s="3">
-        <v>139964</v>
+        <v>102077</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="E120" s="11"/>
-      <c r="F120" s="5">
-        <v>28.99</v>
+        <v>166</v>
+      </c>
+      <c r="E120" s="13"/>
+      <c r="F120" s="9">
+        <v>189.99</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C121" s="3">
+        <v>109729</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E121" s="13"/>
+      <c r="F121" s="9">
+        <v>109.99</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C122" s="3">
-        <v>104931</v>
+        <v>295198</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="E122" s="11"/>
-      <c r="F122" s="5">
-        <v>6.99</v>
+        <v>169</v>
+      </c>
+      <c r="E122" s="13"/>
+      <c r="F122" s="9">
+        <v>11.69</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C123" s="3">
-        <v>104944</v>
+        <v>102036</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E123" s="11"/>
-      <c r="F123" s="5">
-        <v>12.99</v>
+        <v>170</v>
+      </c>
+      <c r="E123" s="13"/>
+      <c r="F123" s="9">
+        <v>24.99</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C124" s="3">
-        <v>105010</v>
+        <v>139964</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E124" s="11"/>
-      <c r="F124" s="5">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C125" s="3">
-        <v>105001</v>
-      </c>
-      <c r="D125" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E125" s="11"/>
-      <c r="F125" s="5">
-        <v>2.99</v>
+      <c r="E124" s="13"/>
+      <c r="F124" s="9">
+        <v>28.99</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C126" s="3">
-        <v>104862</v>
+        <v>104931</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="E126" s="11"/>
-      <c r="F126" s="5">
-        <v>2.99</v>
+        <v>174</v>
+      </c>
+      <c r="E126" s="13"/>
+      <c r="F126" s="9">
+        <v>6.99</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C127" s="3">
-        <v>104961</v>
+        <v>104944</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="E127" s="11"/>
-      <c r="F127" s="5">
-        <v>4.99</v>
+        <v>175</v>
+      </c>
+      <c r="E127" s="13"/>
+      <c r="F127" s="9">
+        <v>12.99</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C128" s="3">
-        <v>104919</v>
+        <v>105010</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="E128" s="11"/>
-      <c r="F128" s="5">
-        <v>2.59</v>
+        <v>177</v>
+      </c>
+      <c r="E128" s="13"/>
+      <c r="F128" s="9">
+        <v>2.99</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C129" s="3">
-        <v>104992</v>
+        <v>105001</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="E129" s="11"/>
-      <c r="F129" s="5">
+        <v>178</v>
+      </c>
+      <c r="E129" s="13"/>
+      <c r="F129" s="9">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C130" s="3">
+        <v>104862</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E130" s="13"/>
+      <c r="F130" s="9">
         <v>2.99</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C131" s="3">
-        <v>328966</v>
+        <v>104961</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E131" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="F131" s="5">
-        <v>17.989999999999998</v>
+      <c r="E131" s="13"/>
+      <c r="F131" s="9">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C132" s="3">
+        <v>104919</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E132" s="13"/>
+      <c r="F132" s="9">
+        <v>2.59</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C133" s="3">
-        <v>100426</v>
+        <v>104992</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E133" s="11"/>
-      <c r="F133" s="5">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C134" s="3">
-        <v>100431</v>
-      </c>
-      <c r="D134" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="E134" s="11"/>
-      <c r="F134" s="5">
-        <v>7.19</v>
+      <c r="E133" s="13"/>
+      <c r="F133" s="9">
+        <v>2.99</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C135" s="3">
-        <v>133368</v>
+        <v>328966</v>
       </c>
       <c r="D135" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="E135" s="11"/>
-      <c r="F135" s="5">
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C136" s="3">
-        <v>107393</v>
-      </c>
-      <c r="D136" s="4" t="s">
+      <c r="E135" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="E136" s="11" t="s">
+      <c r="F135" s="9">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="F136" s="5">
-        <v>11.49</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A137" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>189</v>
       </c>
       <c r="C137" s="3">
-        <v>100279</v>
+        <v>100426</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E137" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="F137" s="5">
-        <v>10.99</v>
+      <c r="E137" s="13"/>
+      <c r="F137" s="9">
+        <v>3.69</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>189</v>
       </c>
       <c r="C138" s="3">
-        <v>142863</v>
+        <v>100431</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="E138" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="F138" s="5">
-        <v>12.69</v>
+        <v>191</v>
+      </c>
+      <c r="E138" s="13"/>
+      <c r="F138" s="9">
+        <v>7.19</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B139" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C139" s="3">
+        <v>133368</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E139" s="13"/>
+      <c r="F139" s="9">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C140" s="3">
+        <v>107393</v>
+      </c>
+      <c r="D140" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C139" s="3">
-        <v>207586</v>
-      </c>
-      <c r="D139" s="4" t="s">
+      <c r="E140" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="E139" s="11" t="s">
+      <c r="F140" s="9">
+        <v>11.49</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="F139" s="5">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A140" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C140" s="3">
-        <v>100391</v>
-      </c>
-      <c r="D140" s="4" t="s">
+      <c r="C141" s="3">
+        <v>100279</v>
+      </c>
+      <c r="D141" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E140" s="11" t="s">
+      <c r="E141" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="F140" s="5">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C141" s="3">
-        <v>100511</v>
-      </c>
-      <c r="D141" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E141" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="F141" s="5">
-        <v>3.89</v>
+      <c r="F141" s="9">
+        <v>10.99</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C142" s="3">
-        <v>156422</v>
+        <v>142863</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E142" s="11"/>
-      <c r="F142" s="5">
-        <v>5.99</v>
+        <v>199</v>
+      </c>
+      <c r="E142" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="F142" s="9">
+        <v>12.69</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B143" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C143" s="3">
+        <v>207586</v>
+      </c>
+      <c r="D143" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C143" s="3">
-        <v>290791</v>
-      </c>
-      <c r="D143" s="4" t="s">
+      <c r="E143" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="F143" s="9">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C144" s="3">
+        <v>100391</v>
+      </c>
+      <c r="D144" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="E143" s="11" t="s">
+      <c r="E144" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="F143" s="5">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C144" s="3">
-        <v>326954</v>
-      </c>
-      <c r="D144" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="E144" s="11"/>
-      <c r="F144" s="5">
-        <v>8.99</v>
+      <c r="F144" s="9">
+        <v>2.69</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>206</v>
       </c>
       <c r="C145" s="3">
-        <v>257710</v>
+        <v>100511</v>
       </c>
       <c r="D145" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E145" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="E145" s="11"/>
-      <c r="F145" s="5">
-        <v>11.99</v>
+      <c r="F145" s="9">
+        <v>3.89</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C146" s="3">
-        <v>263649</v>
+        <v>156422</v>
       </c>
       <c r="D146" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E146" s="13"/>
+      <c r="F146" s="9">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E146" s="11"/>
-      <c r="F146" s="5">
-        <v>17.989999999999998</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="C147" s="3">
-        <v>228234</v>
+        <v>290791</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E147" s="11"/>
-      <c r="F147" s="5">
-        <v>13.99</v>
+        <v>211</v>
+      </c>
+      <c r="E147" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="F147" s="9">
+        <v>12.99</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C148" s="3">
-        <v>286232</v>
+        <v>326954</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="E148" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="F148" s="5">
-        <v>5.49</v>
+        <v>214</v>
+      </c>
+      <c r="E148" s="13"/>
+      <c r="F148" s="9">
+        <v>8.99</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C149" s="3">
-        <v>286199</v>
+        <v>257710</v>
       </c>
       <c r="D149" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E149" s="13"/>
+      <c r="F149" s="9">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B150" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E149" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="F149" s="5">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C150" s="3">
-        <v>150356</v>
-      </c>
-      <c r="D150" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="E150" s="11"/>
-      <c r="F150" s="5">
-        <v>46.99</v>
+      <c r="C150" s="6">
+        <v>261980</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E150" s="15"/>
+      <c r="F150" s="11">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C151" s="3">
+        <v>263649</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E151" s="13"/>
+      <c r="F151" s="9">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C152" s="3">
+        <v>228234</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E152" s="13"/>
+      <c r="F152" s="9">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C153" s="3">
+        <v>286199</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="E153" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="F153" s="9">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C154" s="3">
+        <v>150356</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E154" s="13"/>
+      <c r="F154" s="9">
+        <v>46.99</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C155" s="3">
         <v>100373</v>
       </c>
-      <c r="D151" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E151" s="11"/>
-      <c r="F151" s="5">
+      <c r="D155" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E155" s="13"/>
+      <c r="F155" s="9">
         <v>23.99</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B153" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C153" s="7">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C157" s="3">
         <v>252582</v>
       </c>
-      <c r="D153" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="E153" s="12"/>
-      <c r="F153" s="9">
+      <c r="D157" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E157" s="13"/>
+      <c r="F157" s="9">
         <v>38.99</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="C155" s="7">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C159" s="3">
         <v>105838</v>
       </c>
-      <c r="D155" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="E155" s="12"/>
-      <c r="F155" s="9">
+      <c r="D159" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E159" s="13"/>
+      <c r="F159" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A156" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="C156" s="7">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C160" s="3">
         <v>105840</v>
       </c>
-      <c r="D156" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="E156" s="12"/>
-      <c r="F156" s="9">
+      <c r="D160" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E160" s="13"/>
+      <c r="F160" s="9">
         <v>15.99</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B157" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="C157" s="7">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C161" s="3">
         <v>109597</v>
       </c>
-      <c r="D157" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="E157" s="12"/>
-      <c r="F157" s="9">
-        <v>17.989999999999998</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="C158" s="7">
-        <v>119927</v>
-      </c>
-      <c r="D158" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="E158" s="12"/>
-      <c r="F158" s="9">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B159" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C159" s="7">
-        <v>105788</v>
-      </c>
-      <c r="D159" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="E159" s="12"/>
-      <c r="F159" s="9">
-        <v>28.99</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B160" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C160" s="7">
-        <v>329843</v>
-      </c>
-      <c r="D160" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="E160" s="12"/>
-      <c r="F160" s="9">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B161" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C161" s="7">
-        <v>228422</v>
-      </c>
-      <c r="D161" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="E161" s="12"/>
+      <c r="D161" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E161" s="13"/>
       <c r="F161" s="9">
         <v>17.989999999999998</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B162" s="6" t="s">
+      <c r="A162" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C162" s="3">
+        <v>119927</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E162" s="13"/>
+      <c r="F162" s="9">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C163" s="3">
+        <v>105788</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E163" s="13"/>
+      <c r="F163" s="9">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C164" s="3">
+        <v>329843</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="E164" s="13"/>
+      <c r="F164" s="9">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C165" s="3">
+        <v>228422</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E165" s="13"/>
+      <c r="F165" s="9">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C166" s="3">
+        <v>189031</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E166" s="13"/>
+      <c r="F166" s="9">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C167" s="3">
+        <v>105765</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E167" s="13"/>
+      <c r="F167" s="9">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C168" s="3">
+        <v>129516</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E168" s="13"/>
+      <c r="F168" s="9">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C169" s="3">
+        <v>132881</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E169" s="13"/>
+      <c r="F169" s="9">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C171" s="3">
+        <v>268136</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E171" s="13"/>
+      <c r="F171" s="9">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C172" s="3">
+        <v>276943</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E172" s="13"/>
+      <c r="F172" s="9">
+        <v>14.49</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C173" s="3">
+        <v>246975</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E173" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="F173" s="9">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B174" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C162" s="7">
-        <v>189031</v>
-      </c>
-      <c r="D162" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="E162" s="12"/>
-      <c r="F162" s="9">
-        <v>17.989999999999998</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B163" s="6" t="s">
+      <c r="C174" s="3">
+        <v>222974</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E174" s="13"/>
+      <c r="F174" s="9">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B175" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C163" s="7">
-        <v>105765</v>
-      </c>
-      <c r="D163" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="E163" s="12"/>
-      <c r="F163" s="9">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B164" s="6" t="s">
+      <c r="C175" s="3">
+        <v>332779</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E175" s="13"/>
+      <c r="F175" s="9">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B176" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C164" s="7">
-        <v>129516</v>
-      </c>
-      <c r="D164" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="E164" s="12"/>
-      <c r="F164" s="9">
-        <v>28.99</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B165" s="6" t="s">
+      <c r="C176" s="3">
+        <v>156502</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E176" s="13"/>
+      <c r="F176" s="9">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B177" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C165" s="7">
-        <v>132881</v>
-      </c>
-      <c r="D165" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="E165" s="12"/>
-      <c r="F165" s="9">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B167" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="C167" s="7">
-        <v>268136</v>
-      </c>
-      <c r="D167" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="E167" s="12"/>
-      <c r="F167" s="9">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B168" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="C168" s="7">
-        <v>276943</v>
-      </c>
-      <c r="D168" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="E168" s="12"/>
-      <c r="F168" s="9">
-        <v>14.49</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A169" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B169" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="C169" s="7">
-        <v>246975</v>
-      </c>
-      <c r="D169" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="E169" s="12" t="s">
+      <c r="C177" s="3">
+        <v>155246</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="E177" s="13"/>
+      <c r="F177" s="9">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="F169" s="9">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B170" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="C170" s="7">
-        <v>101874</v>
-      </c>
-      <c r="D170" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="E170" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="F170" s="9">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B171" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C171" s="7">
-        <v>222974</v>
-      </c>
-      <c r="D171" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="E171" s="12"/>
-      <c r="F171" s="9">
-        <v>7.49</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A172" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B172" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C172" s="7">
-        <v>332779</v>
-      </c>
-      <c r="D172" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="E172" s="12"/>
-      <c r="F172" s="9">
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A173" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B173" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C173" s="7">
-        <v>156502</v>
-      </c>
-      <c r="D173" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="E173" s="12"/>
-      <c r="F173" s="9">
-        <v>40.5</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A174" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B174" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C174" s="7">
-        <v>155246</v>
-      </c>
-      <c r="D174" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="E174" s="12"/>
-      <c r="F174" s="9">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A176" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B176" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C176" s="7">
+      <c r="B179" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C179" s="3">
         <v>215182</v>
       </c>
-      <c r="D176" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="E176" s="12"/>
-      <c r="F176" s="9">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A178" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B178" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="C178" s="7">
-        <v>108785</v>
-      </c>
-      <c r="D178" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="E178" s="12"/>
-      <c r="F178" s="9">
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A179" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B179" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="C179" s="7">
-        <v>108774</v>
-      </c>
-      <c r="D179" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="E179" s="12"/>
+      <c r="D179" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E179" s="13"/>
       <c r="F179" s="9">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A180" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B180" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C180" s="7">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C181" s="3">
+        <v>108785</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E181" s="13"/>
+      <c r="F181" s="9">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C182" s="3">
+        <v>108774</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E182" s="13"/>
+      <c r="F182" s="9">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C183" s="3">
         <v>227259</v>
       </c>
-      <c r="D180" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="E180" s="12"/>
-      <c r="F180" s="9">
+      <c r="D183" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E183" s="13"/>
+      <c r="F183" s="9">
         <v>6.79</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A181" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B181" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="C181" s="7">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C184" s="3">
         <v>138538</v>
       </c>
-      <c r="D181" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="E181" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="F181" s="9">
+      <c r="D184" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E184" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="F184" s="9">
         <v>8.19</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A183" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B183" s="6" t="s">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B186" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C183" s="7">
+      <c r="C186" s="3">
         <v>242795</v>
       </c>
-      <c r="D183" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="E183" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="F183" s="9">
+      <c r="D186" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E186" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="F186" s="9">
         <v>25.99</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B184" s="6" t="s">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B187" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C184" s="7">
+      <c r="C187" s="3">
         <v>289007</v>
       </c>
-      <c r="D184" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="E184" s="12"/>
-      <c r="F184" s="9">
+      <c r="D187" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E187" s="13"/>
+      <c r="F187" s="9">
         <v>36</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A185" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B185" s="6" t="s">
+    <row r="188" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B188" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C185" s="7">
+      <c r="C188" s="3">
         <v>138139</v>
       </c>
-      <c r="D185" s="8" t="s">
+      <c r="D188" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E188" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="F188" s="9">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="E185" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="F185" s="9">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A186" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B186" s="6" t="s">
+      <c r="B189" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C186" s="7">
+      <c r="C189" s="3">
         <v>156523</v>
       </c>
-      <c r="D186" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="E186" s="12"/>
-      <c r="F186" s="9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B187" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C187" s="7">
-        <v>297570</v>
-      </c>
-      <c r="D187" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="E187" s="12"/>
-      <c r="F187" s="9">
-        <v>15.99</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B188" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C188" s="7">
-        <v>308560</v>
-      </c>
-      <c r="D188" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="E188" s="12"/>
-      <c r="F188" s="9">
-        <v>15.99</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A189" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B189" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C189" s="7">
-        <v>255029</v>
-      </c>
-      <c r="D189" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="E189" s="12"/>
+      <c r="D189" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="E189" s="13"/>
       <c r="F189" s="9">
         <v>16</v>
       </c>
     </row>
-    <row r="190" spans="1:6" ht="36" x14ac:dyDescent="0.25">
-      <c r="A190" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B190" s="6" t="s">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B190" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C190" s="7">
-        <v>110941</v>
-      </c>
-      <c r="D190" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="E190" s="12" t="s">
+      <c r="C190" s="3">
+        <v>297570</v>
+      </c>
+      <c r="D190" s="4" t="s">
         <v>266</v>
       </c>
+      <c r="E190" s="13"/>
       <c r="F190" s="9">
         <v>15.99</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A191" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B191" s="6" t="s">
+      <c r="A191" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B191" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C191" s="7">
+      <c r="C191" s="3">
+        <v>297599</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E191" s="13"/>
+      <c r="F191" s="9">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C192" s="3">
         <v>277148</v>
       </c>
-      <c r="D191" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="E191" s="12"/>
-      <c r="F191" s="9">
-        <v>15.99</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A192" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B192" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C192" s="7">
-        <v>200175</v>
-      </c>
-      <c r="D192" s="8" t="s">
+      <c r="D192" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="E192" s="12"/>
+      <c r="E192" s="13" t="s">
+        <v>269</v>
+      </c>
       <c r="F192" s="9">
         <v>15.99</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A193" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B193" s="6" t="s">
+      <c r="A193" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B193" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C193" s="7">
+      <c r="C193" s="3">
+        <v>255029</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E193" s="13"/>
+      <c r="F193" s="9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C194" s="3">
         <v>162945</v>
       </c>
-      <c r="D193" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="E193" s="12"/>
-      <c r="F193" s="9">
+      <c r="D194" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E194" s="13"/>
+      <c r="F194" s="9">
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A194" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B194" s="6" t="s">
+    <row r="195" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A195" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B195" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C194" s="7">
-        <v>297599</v>
-      </c>
-      <c r="D194" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="E194" s="12"/>
-      <c r="F194" s="9">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A195" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B195" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C195" s="7">
+      <c r="C195" s="3">
         <v>161653</v>
       </c>
-      <c r="D195" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="E195" s="12" t="s">
+      <c r="D195" s="4" t="s">
         <v>272</v>
+      </c>
+      <c r="E195" s="13" t="s">
+        <v>273</v>
       </c>
       <c r="F195" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="180" x14ac:dyDescent="0.25">
-      <c r="A196" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B196" s="6" t="s">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B196" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C196" s="7">
+      <c r="C196" s="3">
         <v>215573</v>
       </c>
-      <c r="D196" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E196" s="12" t="s">
+      <c r="D196" s="4" t="s">
         <v>274</v>
       </c>
+      <c r="E196" s="13"/>
       <c r="F196" s="9">
         <v>12</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A197" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B197" s="6" t="s">
+      <c r="A197" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B197" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C197" s="7">
+      <c r="C197" s="3">
         <v>182034</v>
       </c>
-      <c r="D197" s="8" t="s">
+      <c r="D197" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="E197" s="12"/>
+      <c r="E197" s="13"/>
       <c r="F197" s="9">
         <v>14.99</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A198" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B198" s="6" t="s">
+      <c r="A198" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B198" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C198" s="7">
+      <c r="C198" s="3">
         <v>314034</v>
       </c>
-      <c r="D198" s="8" t="s">
+      <c r="D198" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="E198" s="12"/>
+      <c r="E198" s="13"/>
       <c r="F198" s="9">
         <v>10.99</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A199" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B199" s="6" t="s">
+      <c r="A199" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B199" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C199" s="7">
+      <c r="C199" s="3">
         <v>313968</v>
       </c>
-      <c r="D199" s="8" t="s">
+      <c r="D199" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="E199" s="12" t="s">
+      <c r="E199" s="13" t="s">
         <v>279</v>
       </c>
       <c r="F199" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="200" spans="1:6" ht="36" x14ac:dyDescent="0.25">
-      <c r="A200" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B200" s="6" t="s">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C200" s="6">
+        <v>208281</v>
+      </c>
+      <c r="D200" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="C200" s="7">
+      <c r="E200" s="15"/>
+      <c r="F200" s="11">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C201" s="3">
         <v>258213</v>
       </c>
-      <c r="D200" s="8" t="s">
+      <c r="D201" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="E201" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="F201" s="9">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B202" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E200" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="F200" s="9">
-        <v>28.99</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A201" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B201" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="C201" s="7">
+      <c r="C202" s="3">
         <v>229916</v>
       </c>
-      <c r="D201" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="E201" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="F201" s="9">
+      <c r="D202" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E202" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="F202" s="9">
         <v>49.99</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B202" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="C202" s="7">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C203" s="3">
         <v>199322</v>
       </c>
-      <c r="D202" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="E202" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="F202" s="9">
+      <c r="D203" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E203" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="F203" s="9">
         <v>9.99</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A203" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B203" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="C203" s="7">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C204" s="3">
         <v>227236</v>
       </c>
-      <c r="D203" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="E203" s="12"/>
-      <c r="F203" s="9">
+      <c r="D204" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="E204" s="13"/>
+      <c r="F204" s="9">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="204" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A204" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B204" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="C204" s="7">
+    <row r="205" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A205" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C205" s="3">
         <v>109064</v>
       </c>
-      <c r="D204" s="8" t="s">
+      <c r="D205" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E205" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="F205" s="9">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B206" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="E204" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="F204" s="9">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A205" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B205" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="C205" s="7">
+      <c r="C206" s="3">
         <v>256740</v>
       </c>
-      <c r="D205" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="E205" s="12"/>
-      <c r="F205" s="9">
+      <c r="D206" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E206" s="13"/>
+      <c r="F206" s="9">
         <v>9.6</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B206" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="C206" s="7">
+    <row r="207" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A207" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C207" s="3">
         <v>242760</v>
       </c>
-      <c r="D206" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="E206" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="F206" s="9">
+      <c r="D207" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="E207" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="F207" s="9">
         <v>8</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A207" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B207" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="C207" s="7">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C208" s="3">
         <v>242759</v>
       </c>
-      <c r="D207" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="E207" s="12"/>
-      <c r="F207" s="9">
+      <c r="D208" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E208" s="13"/>
+      <c r="F208" s="9">
         <v>7.59</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A208" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B208" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="C208" s="7">
-        <v>108866</v>
-      </c>
-      <c r="D208" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="E208" s="12"/>
-      <c r="F208" s="9">
-        <v>3.76</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A209" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B209" s="6" t="s">
+    <row r="209" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A209" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B209" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="C209" s="7">
-        <v>187000</v>
-      </c>
-      <c r="D209" s="8" t="s">
+      <c r="C209" s="6">
+        <v>103700</v>
+      </c>
+      <c r="D209" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E209" s="12" t="s">
+      <c r="E209" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="F209" s="9">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A211" s="2" t="s">
+      <c r="F209" s="11">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B210" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B211" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C211" s="3">
-        <v>100886</v>
-      </c>
-      <c r="D211" s="4" t="s">
+      <c r="C210" s="6">
+        <v>265970</v>
+      </c>
+      <c r="D210" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="E211" s="11" t="s">
+      <c r="E210" s="15"/>
+      <c r="F210" s="11">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C211" s="6">
+        <v>104371</v>
+      </c>
+      <c r="D211" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="F211" s="5">
-        <v>4.49</v>
+      <c r="E211" s="15"/>
+      <c r="F211" s="11">
+        <v>9.99</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>300</v>
+        <v>259</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>303</v>
       </c>
       <c r="C212" s="3">
-        <v>237472</v>
+        <v>108866</v>
       </c>
       <c r="D212" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="E212" s="11"/>
-      <c r="F212" s="5">
+      <c r="E212" s="13"/>
+      <c r="F212" s="9">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C213" s="3">
+        <v>187000</v>
+      </c>
+      <c r="D213" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="E213" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="F213" s="9">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C215" s="3">
+        <v>100886</v>
+      </c>
+      <c r="D215" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E215" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="F215" s="9">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C216" s="3">
+        <v>237472</v>
+      </c>
+      <c r="D216" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="E216" s="13"/>
+      <c r="F216" s="9">
         <v>1.99</v>
       </c>
     </row>
-    <row r="213" spans="1:6" ht="48" x14ac:dyDescent="0.25">
-      <c r="A213" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C213" s="3">
+    <row r="217" spans="1:6" ht="48" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C217" s="3">
         <v>108412</v>
       </c>
-      <c r="D213" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="E213" s="11" t="s">
-        <v>306</v>
-      </c>
-      <c r="F213" s="5">
+      <c r="D217" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="E217" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F217" s="9">
         <v>1.99</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="36" x14ac:dyDescent="0.25">
-      <c r="A215" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C215" s="3">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C219" s="3">
         <v>285689</v>
       </c>
-      <c r="D215" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E215" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="F215" s="5">
+      <c r="D219" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="E219" s="13"/>
+      <c r="F219" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="216" spans="1:6" ht="36" x14ac:dyDescent="0.25">
-      <c r="A216" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="B216" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C216" s="7">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C220" s="3">
         <v>186012</v>
       </c>
-      <c r="D216" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="E216" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="F216" s="9">
+      <c r="D220" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E220" s="13"/>
+      <c r="F220" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="217" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A217" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="B217" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C217" s="7">
+    <row r="221" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A221" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C221" s="3">
         <v>123791</v>
       </c>
-      <c r="D217" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="E217" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="F217" s="9">
+      <c r="D221" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="E221" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="F221" s="9">
         <v>9.99</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A218" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="B218" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="C218" s="7">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C222" s="3">
         <v>200131</v>
       </c>
-      <c r="D218" s="8" t="s">
+      <c r="D222" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E222" s="13"/>
+      <c r="F222" s="9">
+        <v>36.99</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="E218" s="12"/>
-      <c r="F218" s="9">
-        <v>36.99</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A219" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="B219" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C219" s="7">
+      <c r="B223" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C223" s="3">
         <v>118939</v>
       </c>
-      <c r="D219" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="E219" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="F219" s="9">
+      <c r="D223" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="E223" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="F223" s="9">
         <v>3.59</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="72" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
-    <oddHeader>&amp;LBLACK FRIDAY 25-11-2025&amp;C&amp;P - &amp;N</oddHeader>
+    <oddHeader>&amp;LBLACK FRIDAY - 26-11-2025&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - BLACK - JARDEL.xlsx
+++ b/giro_da_praça_ofertas - BLACK - JARDEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34DDEC7-951F-468C-B711-D3D507BE791C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F4E0C0-93E0-4090-99E2-37AB16B8D520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="345">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -103,9 +103,6 @@
     <t>MÁSCARA CAPILAR CHIKAS 700G</t>
   </si>
   <si>
-    <t>ACORDA CACHOS ARIBA, ADIOS QUEDA, CRESCE E APARECE, CRESPO PODEROSO, DELETA DANOS, DESLIZA LISO, HIDRATA CABELOS</t>
-  </si>
-  <si>
     <t>MÁSCARA CAPILAR CHIKAS 700G MATIZA LOIRO</t>
   </si>
   <si>
@@ -154,10 +151,10 @@
     <t>#08 BAZAR - UTENSÍLIOS DE COZINHA / TÉRMICOS</t>
   </si>
   <si>
-    <t>GARRAFA TERMICA TERMOLAR 1L</t>
-  </si>
-  <si>
-    <t>PERSONAL PRETA, PERSONAL VERMELHA</t>
+    <t>GARRAFA TERMICA TERMOLAR PERSONAL 1L</t>
+  </si>
+  <si>
+    <t>PRETA, VERMELHA</t>
   </si>
   <si>
     <t>GARRAFÃO TERMICO TERMOLAR 5L</t>
@@ -184,9 +181,6 @@
     <t>ESMALTE RISQUE 7,5ML</t>
   </si>
   <si>
-    <t>DIAMOND GEL TOP COAT FIXADOR, GUERREIRA DO ARCO IRIS</t>
-  </si>
-  <si>
     <t>ESMALTE RISQUE 8ML</t>
   </si>
   <si>
@@ -265,9 +259,6 @@
     <t>CHOCOLATE EM BARRA NEUGEBAUER 80G</t>
   </si>
   <si>
-    <t>AMENDOIN, AO LEITE, BRANCO, CARAMELO, COOKIES, FLOCOS, MEIO AMA, PRETO BRANCO</t>
-  </si>
-  <si>
     <t>DOCE DE LEITE PIRACANJUBA 350G ZERO LACTOSE</t>
   </si>
   <si>
@@ -421,6 +412,66 @@
     <t xml:space="preserve">MASSA PARA LASANHA FORTALEZA 500G SEMOLA </t>
   </si>
   <si>
+    <t>BLACK MATRIZ 28/11/25 - ACOUGUE</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - #02 BOVINA</t>
+  </si>
+  <si>
+    <t>ALCATRA BOVINA KG</t>
+  </si>
+  <si>
+    <t>BISTECA BOVINA DO ACÉM KG</t>
+  </si>
+  <si>
+    <t>BISTECA BOVINA DO CONTRA FILE KG</t>
+  </si>
+  <si>
+    <t>CARNE BOVINA SERENADA KG</t>
+  </si>
+  <si>
+    <t>CARNE DE SOL KG SEGUNDA</t>
+  </si>
+  <si>
+    <t>CARNE MOIDA KG</t>
+  </si>
+  <si>
+    <t>CHAMBARI KG</t>
+  </si>
+  <si>
+    <t>CONTRA FILÉ KG</t>
+  </si>
+  <si>
+    <t>COSTELA BOVINA KG</t>
+  </si>
+  <si>
+    <t>COXÃO MOLE KG</t>
+  </si>
+  <si>
+    <t>SUINO CAIPIRA KG</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - #03 SUÍNA</t>
+  </si>
+  <si>
+    <t>BISTECA SUINA CARRE KG</t>
+  </si>
+  <si>
+    <t>BISTECA SUINA DO PERNIL KG</t>
+  </si>
+  <si>
+    <t>INGREDIENTES PARA FEIJOADA KG</t>
+  </si>
+  <si>
+    <t>PANCETA SUINA KG</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+  </si>
+  <si>
+    <t>LINGUIÇA CASEIRA BOVINA KG</t>
+  </si>
+  <si>
     <t>BLACK MATRIZ 28/11/25 - BEBIDAS</t>
   </si>
   <si>
@@ -433,10 +484,10 @@
     <t>REFRIGERANTE COCA COLA 2L</t>
   </si>
   <si>
-    <t>REFRIGERANTE FANTA 2L LARANJA</t>
-  </si>
-  <si>
-    <t>REFRIGERANTE FANTA 2L UVA</t>
+    <t>REFRIGERANTE FANTA 2L</t>
+  </si>
+  <si>
+    <t>LARANJA, UVA</t>
   </si>
   <si>
     <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
@@ -445,9 +496,6 @@
     <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
   </si>
   <si>
-    <t>ENERGETICO EXTRA POWER 270ML</t>
-  </si>
-  <si>
     <t>ENERGETICO EXTRA POWER 2L</t>
   </si>
   <si>
@@ -535,7 +583,55 @@
     <t>VINHO GALIOTTO 1L TINTO SUAVE</t>
   </si>
   <si>
-    <t>VINHO PERGOLA 1L TINTO SUAVE</t>
+    <t>BLACK MATRIZ 28/11/25 - HASKELL</t>
+  </si>
+  <si>
+    <t>CONDICIONADOR HASKELL 500G ROSA MOSQUETA</t>
+  </si>
+  <si>
+    <t>CREME FINALIZADOR DE CRESPOS HASKELL 500G MANTEIGA DE MURU</t>
+  </si>
+  <si>
+    <t>CREME PARA PENTEAR HASKELL 500G SE CURVE CACHOS</t>
+  </si>
+  <si>
+    <t>FINALIZADOR HASKELL 500G CURVA E COLA</t>
+  </si>
+  <si>
+    <t>GOMA TEXTURIZADA HASKELL 500G GOMAS DE TAPIOCA E LINHAÇA</t>
+  </si>
+  <si>
+    <t>KIT SHAMPOO E CONDICIONADOR HASKELL 1KIT</t>
+  </si>
+  <si>
+    <t>MANDIOCA, MURUMURU</t>
+  </si>
+  <si>
+    <t>KIT SHAMPOO E CONDICIONADOR HASKELL 1KIT CAVALO FORTE</t>
+  </si>
+  <si>
+    <t>KIT SHAMPOO E CONDICIONADOR HASKELL 1KIT SOS VERÃO</t>
+  </si>
+  <si>
+    <t>KIT SHAMPOO E CONDICIONADOR HASKELL 500ML MANDIOCA</t>
+  </si>
+  <si>
+    <t>KIT SHAMPOO E CONDICIONADOR HASKELL 500ML MURUMURU</t>
+  </si>
+  <si>
+    <t>MASCARA CAPILAR HASKELL 500G</t>
+  </si>
+  <si>
+    <t>KARITE CUPUACU E MURUMURU, MANTEIGA DE MANGA, OLEOS DE RICINO PEQUI E MACADAMIA</t>
+  </si>
+  <si>
+    <t>MODELADOR DE CACHOS HASKELL 500G BABOSA E MANTEIGA DE PISTACHE</t>
+  </si>
+  <si>
+    <t>MÁSCARA CAPILAR CAVALO FORTE HASKELL 900G</t>
+  </si>
+  <si>
+    <t>SHAMPOO HASKELL 500G ROSA MOSQUETA E ÓLEO DE RICINO</t>
   </si>
   <si>
     <t>BLACK MATRIZ 28/11/25 - HORTIFRUTI</t>
@@ -544,12 +640,12 @@
     <t>#09 HORTIFRUTI - FRUTAS</t>
   </si>
   <si>
+    <t>BANANA PRATA KG</t>
+  </si>
+  <si>
     <t>LARANJA KG</t>
   </si>
   <si>
-    <t>MAÇÃ NACIONAL KG</t>
-  </si>
-  <si>
     <t>#09 HORTIFRUTI - LEGUMES E TUBÉRCULOS</t>
   </si>
   <si>
@@ -577,15 +673,6 @@
     <t>REPOLHO VERDE KG</t>
   </si>
   <si>
-    <t>#10 OVOS</t>
-  </si>
-  <si>
-    <t>OVOS DE GRANJA IANA BDJ 30UN</t>
-  </si>
-  <si>
-    <t>BRANCOS, BRANCOS GRANDES</t>
-  </si>
-  <si>
     <t>BLACK MATRIZ 28/11/25 - LIMPEZA</t>
   </si>
   <si>
@@ -607,48 +694,30 @@
     <t>AMACIANTE DE ROUPAS YPÊ 2L</t>
   </si>
   <si>
-    <t>ACONCHEGO, INTENSO</t>
-  </si>
-  <si>
     <t>#03 LIMPEZA - DESINFETANTES</t>
   </si>
   <si>
     <t>DESINFETANTE PINHO BRIL 1L</t>
   </si>
   <si>
-    <t>BRISA MAR, CAMPOS DE LAVANDA, FLORES DE LIMÃO, PLUS</t>
-  </si>
-  <si>
     <t>DESINFETANTE YPÊ BAK 2L</t>
   </si>
   <si>
-    <t>EUCALIPTO, FLORAL, LAVANDA</t>
-  </si>
-  <si>
     <t>#03 LIMPEZA - DETERGENTES</t>
   </si>
   <si>
     <t>DETERGENTE LIQUIDO LAVABEM 500ML</t>
   </si>
   <si>
-    <t>CLEAR, COCO, LIMÃO, MAÇÃ, NEUTRO</t>
-  </si>
-  <si>
     <t>DETERGENTE LIQUIDO YPÊ 500ML</t>
   </si>
   <si>
-    <t>CAPIM LIMÃO, CLEAR, CLEAR CARE, COCO, LIMAO, MACA, NEUTRO</t>
-  </si>
-  <si>
     <t>#03 LIMPEZA - LIMPA ALUMINIO</t>
   </si>
   <si>
     <t>LIMPA ALUMINIO POLITRIZ 500ML</t>
   </si>
   <si>
-    <t>LIMÃO, TRADICIONAL</t>
-  </si>
-  <si>
     <t>#03 LIMPEZA - LIMPADORES</t>
   </si>
   <si>
@@ -658,9 +727,6 @@
     <t>ODORIZADOR PURA CASA 400ML</t>
   </si>
   <si>
-    <t>AERO AQUAMAR, AERO LAVANDA, AERO TALCO</t>
-  </si>
-  <si>
     <t>#03 LIMPEZA - SABÃO</t>
   </si>
   <si>
@@ -694,6 +760,36 @@
     <t>SODA CAUSTICA SOL 1KG</t>
   </si>
   <si>
+    <t>BLACK MATRIZ 28/11/25 - LP GUIMARAES</t>
+  </si>
+  <si>
+    <t>TEMPERO EM PÓ SAZON SACHÊ 60G</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - MASSAS INSTANTÂNEAS</t>
+  </si>
+  <si>
+    <t>MACARRÃO INSTANTANEO NISSIN LAMEN 85G</t>
+  </si>
+  <si>
+    <t>BLACK MATRIZ 28/11/25 - PADARIA</t>
+  </si>
+  <si>
+    <t>#11 PADARIA</t>
+  </si>
+  <si>
+    <t>BOLO DA VOVÓ KG</t>
+  </si>
+  <si>
+    <t>BOLO DECORADO KG CHANTILLY</t>
+  </si>
+  <si>
+    <t>BOLO DECORADO KG GANACHE</t>
+  </si>
+  <si>
+    <t>PÃO DE FORMA GIRO UM</t>
+  </si>
+  <si>
     <t>BLACK MATRIZ 28/11/25 - PAS PESAVEIS</t>
   </si>
   <si>
@@ -718,9 +814,6 @@
     <t xml:space="preserve">FRANGO AMERICANO KG CONGELADO </t>
   </si>
   <si>
-    <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
-  </si>
-  <si>
     <t>BACON SADIA KG VACUO</t>
   </si>
   <si>
@@ -769,12 +862,12 @@
     <t>REQUEIJÃO BOUA 380G CREMOSO TRADICIONAL</t>
   </si>
   <si>
-    <t xml:space="preserve">REQUEIJÃO CANTO DE MINAS 1,8 KG CREMOSO </t>
-  </si>
-  <si>
     <t>REQUEIJÃO CANTO DE MINAS 200G CREMOSO TRADICIONAL</t>
   </si>
   <si>
+    <t xml:space="preserve">REQUEIJÃO CANTO DE MINAS BISNAGA 1,8 KG CREMOSO </t>
+  </si>
+  <si>
     <t>#05 BEBIDA - #01 POLPAS</t>
   </si>
   <si>
@@ -820,22 +913,13 @@
     <t>CREME PARA PENTEAR TURMA DA XUXINHA BARUEL 150ML CACHOS</t>
   </si>
   <si>
-    <t>KIT SHAMPOO + CONDICIONADOR TURMA DA XUXINHA BARUEL</t>
-  </si>
-  <si>
-    <t>KIT SHAMPOO + CONDICIONADOR TURMA DA XUXINHA BARUEL INFANTIL</t>
-  </si>
-  <si>
-    <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD 1KIT</t>
-  </si>
-  <si>
-    <t>COMPRIDOS E FORTES, DEFESA PROLONGADA, HIDRATANTE ÁGUA COCO, LISO PROLONGADADO, QUERATINA REPARAÇÃO, SALVA FIOS, ÓLEO DE ARGAN</t>
-  </si>
-  <si>
-    <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD 1KIT DETOX</t>
-  </si>
-  <si>
-    <t>KIT SHAMPOO + CONDICONADOR NIELY GOLD 1KIT NUTRIÇÃO PODER</t>
+    <t>KIT SHAMPOO E CONDICIONADOR NIELY GOLD 1KIT</t>
+  </si>
+  <si>
+    <t>KIT SHAMPOO E CONDICIONADOR TURMA DA XUXINHA BARUEL</t>
+  </si>
+  <si>
+    <t>KIT SHAMPOO E CONDICIONADOR TURMA DA XUXINHA BARUEL INFANTIL</t>
   </si>
   <si>
     <t>SHAMPOO TURMA DA XUXINHA BARUEL 120ML</t>
@@ -853,13 +937,10 @@
     <t>DESODORANTE DOVE AEROSOL 150ML ORIGINAL</t>
   </si>
   <si>
-    <t>DESODORANTE HERBISSIMO CREME 55G LAVANDA</t>
-  </si>
-  <si>
     <t>DESODORANTE HERBISSIMO STICK CREME 45G</t>
   </si>
   <si>
-    <t>BIO PROTECT, SENSITIVE, VANILLA</t>
+    <t>BIO PROTECT, LAVANDA, SENSITIVE, VANILLA</t>
   </si>
   <si>
     <t>DESODORANTE MOOD AEROSOL 150ML</t>
@@ -892,9 +973,6 @@
     <t>#04 HIGIENE PESSOAL - INTIMA</t>
   </si>
   <si>
-    <t>ABSORVENTE INTIMUS 16UN 1PCT NOTURNO COM ABAS SUAVE</t>
-  </si>
-  <si>
     <t>ABSORVENTE INTIMUS GEL 8 X 1 1PCT</t>
   </si>
   <si>
@@ -934,7 +1012,7 @@
     <t>#04 HIGIENE PESSOAL - SABONETE</t>
   </si>
   <si>
-    <t>SABONETE PALMOLIVE 150G LEITE E PETALAS ROSA</t>
+    <t>SABONETE REXONA 84G</t>
   </si>
   <si>
     <t>#04 HIGIENE PESSOAL - TALCOS</t>
@@ -955,18 +1033,9 @@
     <t>CARNE, FEIJÃO OVOS E ARROZ, LEGUMES, PEIXES E ARROZ</t>
   </si>
   <si>
-    <t>#02 MERCEARIA - MASSAS INSTANTÂNEAS</t>
-  </si>
-  <si>
-    <t>MACARRÃO INSTANTANEO SANDELLA 75G INFANTIL CARNE</t>
-  </si>
-  <si>
     <t>MACARRÃO INSTANTANEO SANDELLA 85G</t>
   </si>
   <si>
-    <t>CALABRESA PICANTE, CARNE, CARNE COM PIMENTA, CARNE TOMATE, GALINHA, GALINHA CAIPIRA, GALINHA CAIPIRA APIMENTADA</t>
-  </si>
-  <si>
     <t>BLACK MATRIZ 28/11/25 - START QUIMICA</t>
   </si>
   <si>
@@ -979,9 +1048,6 @@
     <t>DESINFETANTE START VOREL 2L</t>
   </si>
   <si>
-    <t>CITRUS, EUCALIPTO, FLORAL, JASMIM, LAVANDA, PINHO</t>
-  </si>
-  <si>
     <t>#03 LIMPEZA - LAVA ROUPAS</t>
   </si>
   <si>
@@ -989,9 +1055,6 @@
   </si>
   <si>
     <t>LIMPA ALUMINIO POLYLAR 500ML</t>
-  </si>
-  <si>
-    <t>LIMÃO, MAÇÃ</t>
   </si>
 </sst>
 </file>
@@ -1126,16 +1189,6 @@
     <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1147,6 +1200,16 @@
     </xf>
     <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1453,15 +1516,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F223"/>
+  <dimension ref="A1:F254"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="56.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.42578125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1477,10 +1540,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1497,8 +1560,8 @@
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="13"/>
-      <c r="F2" s="9">
+      <c r="E2" s="9"/>
+      <c r="F2" s="13">
         <v>20.49</v>
       </c>
     </row>
@@ -1515,8 +1578,8 @@
       <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="9">
+      <c r="E3" s="9"/>
+      <c r="F3" s="13">
         <v>17.989999999999998</v>
       </c>
     </row>
@@ -1533,8 +1596,8 @@
       <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="9">
+      <c r="E4" s="9"/>
+      <c r="F4" s="13">
         <v>14.99</v>
       </c>
     </row>
@@ -1551,8 +1614,8 @@
       <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="9">
+      <c r="E5" s="9"/>
+      <c r="F5" s="13">
         <v>20.99</v>
       </c>
     </row>
@@ -1569,8 +1632,8 @@
       <c r="D6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="9">
+      <c r="E6" s="9"/>
+      <c r="F6" s="13">
         <v>19.989999999999998</v>
       </c>
     </row>
@@ -1587,8 +1650,8 @@
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="9">
+      <c r="E7" s="9"/>
+      <c r="F7" s="13">
         <v>22.99</v>
       </c>
     </row>
@@ -1605,8 +1668,8 @@
       <c r="D8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="9">
+      <c r="E8" s="9"/>
+      <c r="F8" s="13">
         <v>6.99</v>
       </c>
     </row>
@@ -1623,8 +1686,8 @@
       <c r="D9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="9">
+      <c r="E9" s="9"/>
+      <c r="F9" s="13">
         <v>6.99</v>
       </c>
     </row>
@@ -1641,8 +1704,8 @@
       <c r="D10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="9">
+      <c r="E10" s="9"/>
+      <c r="F10" s="13">
         <v>5.49</v>
       </c>
     </row>
@@ -1659,8 +1722,8 @@
       <c r="D11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="9">
+      <c r="E11" s="9"/>
+      <c r="F11" s="13">
         <v>5.99</v>
       </c>
     </row>
@@ -1677,8 +1740,8 @@
       <c r="D12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="9">
+      <c r="E12" s="9"/>
+      <c r="F12" s="13">
         <v>4.99</v>
       </c>
     </row>
@@ -1695,8 +1758,8 @@
       <c r="D13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="9">
+      <c r="E13" s="9"/>
+      <c r="F13" s="13">
         <v>6.99</v>
       </c>
     </row>
@@ -1713,12 +1776,12 @@
       <c r="D14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="9">
+      <c r="E14" s="9"/>
+      <c r="F14" s="13">
         <v>7.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="48" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
@@ -1731,10 +1794,8 @@
       <c r="D16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="9">
+      <c r="E16" s="9"/>
+      <c r="F16" s="13">
         <v>22.99</v>
       </c>
     </row>
@@ -1749,3464 +1810,3946 @@
         <v>318660</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="9">
+        <v>27</v>
+      </c>
+      <c r="E17" s="9"/>
+      <c r="F17" s="13">
         <v>24.99</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="C19" s="3">
         <v>102294</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="9">
+        <v>30</v>
+      </c>
+      <c r="E19" s="9"/>
+      <c r="F19" s="13">
         <v>5.99</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="C20" s="3">
         <v>312887</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="9">
+        <v>31</v>
+      </c>
+      <c r="E20" s="9"/>
+      <c r="F20" s="13">
         <v>5.99</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" s="3">
         <v>189135</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="13"/>
-      <c r="F22" s="9">
+        <v>33</v>
+      </c>
+      <c r="E22" s="9"/>
+      <c r="F22" s="13">
         <v>5.99</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C23" s="3">
         <v>102416</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="13"/>
-      <c r="F23" s="9">
+        <v>35</v>
+      </c>
+      <c r="E23" s="9"/>
+      <c r="F23" s="13">
         <v>5.99</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" s="3">
         <v>302449</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="13"/>
-      <c r="F24" s="9">
+        <v>36</v>
+      </c>
+      <c r="E24" s="9"/>
+      <c r="F24" s="13">
         <v>5.99</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25" s="3">
         <v>311244</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="13"/>
-      <c r="F25" s="9">
+        <v>37</v>
+      </c>
+      <c r="E25" s="9"/>
+      <c r="F25" s="13">
         <v>4.99</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26" s="3">
         <v>113856</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="13"/>
-      <c r="F26" s="9">
+        <v>39</v>
+      </c>
+      <c r="E26" s="9"/>
+      <c r="F26" s="13">
         <v>4.99</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C27" s="3">
         <v>199260</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="13"/>
-      <c r="F27" s="9">
+        <v>40</v>
+      </c>
+      <c r="E27" s="9"/>
+      <c r="F27" s="13">
         <v>49.99</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C28" s="3">
         <v>239161</v>
       </c>
       <c r="D28" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="9"/>
+      <c r="F28" s="13">
+        <v>45.99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="E28" s="13"/>
-      <c r="F28" s="9">
-        <v>45.99</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="C29" s="3">
         <v>134383</v>
       </c>
       <c r="D29" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F29" s="9">
+      <c r="F29" s="13">
         <v>29.99</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30" s="3">
         <v>214439</v>
       </c>
       <c r="D30" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="F30" s="9">
+      <c r="F30" s="13">
         <v>45.99</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="C32" s="3">
         <v>111807</v>
       </c>
       <c r="D32" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32" s="13">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E32" s="13"/>
-      <c r="F32" s="9">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="B34" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="C34" s="3">
         <v>271863</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="F34" s="9">
+        <v>52</v>
+      </c>
+      <c r="E34" s="9"/>
+      <c r="F34" s="13">
         <v>5.49</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="C35" s="3">
         <v>308384</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="9">
+        <v>53</v>
+      </c>
+      <c r="E35" s="9"/>
+      <c r="F35" s="13">
         <v>5.49</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C37" s="3">
         <v>100061</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="9">
+        <v>56</v>
+      </c>
+      <c r="E37" s="9"/>
+      <c r="F37" s="13">
         <v>4.99</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C38" s="3">
         <v>112978</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E38" s="13"/>
-      <c r="F38" s="9">
+        <v>58</v>
+      </c>
+      <c r="E38" s="9"/>
+      <c r="F38" s="13">
         <v>2.89</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C39" s="3">
         <v>128930</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E39" s="13"/>
-      <c r="F39" s="9">
+        <v>59</v>
+      </c>
+      <c r="E39" s="9"/>
+      <c r="F39" s="13">
         <v>6.39</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C40" s="3">
         <v>107361</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E40" s="13"/>
-      <c r="F40" s="9">
+        <v>60</v>
+      </c>
+      <c r="E40" s="9"/>
+      <c r="F40" s="13">
         <v>5.89</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C41" s="3">
         <v>100024</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E41" s="13"/>
-      <c r="F41" s="9">
+        <v>61</v>
+      </c>
+      <c r="E41" s="9"/>
+      <c r="F41" s="13">
         <v>5.69</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C42" s="3">
         <v>100027</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E42" s="13"/>
-      <c r="F42" s="9">
+        <v>62</v>
+      </c>
+      <c r="E42" s="9"/>
+      <c r="F42" s="13">
         <v>7.99</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C43" s="3">
         <v>294705</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E43" s="13"/>
-      <c r="F43" s="9">
+        <v>63</v>
+      </c>
+      <c r="E43" s="9"/>
+      <c r="F43" s="13">
         <v>2.39</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C44" s="3">
         <v>255841</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E44" s="13"/>
-      <c r="F44" s="9">
+        <v>64</v>
+      </c>
+      <c r="E44" s="9"/>
+      <c r="F44" s="13">
         <v>2.89</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C45" s="3">
         <v>100120</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E45" s="13"/>
-      <c r="F45" s="9">
+        <v>65</v>
+      </c>
+      <c r="E45" s="9"/>
+      <c r="F45" s="13">
         <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C46" s="6">
+      <c r="A46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="3">
         <v>149122</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E46" s="15"/>
-      <c r="F46" s="11">
+      <c r="D46" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E46" s="9"/>
+      <c r="F46" s="13">
         <v>6.99</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C47" s="3">
         <v>145874</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E47" s="13"/>
-      <c r="F47" s="9">
+        <v>67</v>
+      </c>
+      <c r="E47" s="9"/>
+      <c r="F47" s="13">
         <v>10.49</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C48" s="3">
         <v>128920</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E48" s="13"/>
-      <c r="F48" s="9">
+        <v>68</v>
+      </c>
+      <c r="E48" s="9"/>
+      <c r="F48" s="13">
         <v>6.99</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C50" s="3">
         <v>255232</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E50" s="13"/>
-      <c r="F50" s="9">
+        <v>71</v>
+      </c>
+      <c r="E50" s="9"/>
+      <c r="F50" s="13">
         <v>18.989999999999998</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C51" s="3">
         <v>101137</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E51" s="13"/>
-      <c r="F51" s="9">
+        <v>72</v>
+      </c>
+      <c r="E51" s="9"/>
+      <c r="F51" s="13">
         <v>14.99</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C52" s="3">
         <v>261728</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E52" s="13"/>
-      <c r="F52" s="9">
+        <v>73</v>
+      </c>
+      <c r="E52" s="9"/>
+      <c r="F52" s="13">
         <v>6.99</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C53" s="3">
         <v>186826</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E53" s="13"/>
-      <c r="F53" s="9">
+        <v>74</v>
+      </c>
+      <c r="E53" s="9"/>
+      <c r="F53" s="13">
         <v>5.39</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C54" s="3">
         <v>250013</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="9">
+        <v>75</v>
+      </c>
+      <c r="E54" s="9"/>
+      <c r="F54" s="13">
         <v>4.99</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C55" s="3">
         <v>286197</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E55" s="13"/>
-      <c r="F55" s="9">
+        <v>76</v>
+      </c>
+      <c r="E55" s="9"/>
+      <c r="F55" s="13">
         <v>8.59</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="36" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C56" s="3">
         <v>297920</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="F56" s="9">
+        <v>78</v>
+      </c>
+      <c r="E56" s="9"/>
+      <c r="F56" s="13">
         <v>6.59</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C57" s="3">
         <v>202443</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="9">
+        <v>79</v>
+      </c>
+      <c r="E57" s="9"/>
+      <c r="F57" s="13">
         <v>11.99</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C58" s="3">
         <v>114256</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="9">
+        <v>81</v>
+      </c>
+      <c r="E58" s="9"/>
+      <c r="F58" s="13">
         <v>17.989999999999998</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C59" s="3">
         <v>273006</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E59" s="13"/>
-      <c r="F59" s="9">
+        <v>82</v>
+      </c>
+      <c r="E59" s="9"/>
+      <c r="F59" s="13">
         <v>6.99</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C60" s="3">
         <v>101874</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F60" s="9">
+        <v>84</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F60" s="13">
         <v>3.19</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C61" s="3">
         <v>101066</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E61" s="13"/>
-      <c r="F61" s="9">
+        <v>87</v>
+      </c>
+      <c r="E61" s="9"/>
+      <c r="F61" s="13">
         <v>3.29</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C62" s="3">
         <v>155079</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E62" s="13"/>
-      <c r="F62" s="9">
+        <v>88</v>
+      </c>
+      <c r="E62" s="9"/>
+      <c r="F62" s="13">
         <v>3.49</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C63" s="3">
         <v>108434</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E63" s="13"/>
-      <c r="F63" s="9">
+        <v>89</v>
+      </c>
+      <c r="E63" s="9"/>
+      <c r="F63" s="13">
         <v>6.99</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C64" s="3">
         <v>101083</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E64" s="13"/>
-      <c r="F64" s="9">
+        <v>90</v>
+      </c>
+      <c r="E64" s="9"/>
+      <c r="F64" s="13">
         <v>6.99</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C65" s="3">
         <v>219003</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E65" s="13"/>
-      <c r="F65" s="9">
+        <v>92</v>
+      </c>
+      <c r="E65" s="9"/>
+      <c r="F65" s="13">
         <v>7.59</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C66" s="3">
         <v>170363</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E66" s="13"/>
-      <c r="F66" s="9">
+        <v>93</v>
+      </c>
+      <c r="E66" s="9"/>
+      <c r="F66" s="13">
         <v>6.19</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C67" s="3">
         <v>106922</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E67" s="13"/>
-      <c r="F67" s="9">
+        <v>95</v>
+      </c>
+      <c r="E67" s="9"/>
+      <c r="F67" s="13">
         <v>41.99</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C68" s="3">
         <v>307145</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E68" s="13"/>
-      <c r="F68" s="9">
+        <v>96</v>
+      </c>
+      <c r="E68" s="9"/>
+      <c r="F68" s="13">
         <v>19.989999999999998</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C70" s="3">
         <v>132657</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E70" s="13"/>
-      <c r="F70" s="9">
+        <v>99</v>
+      </c>
+      <c r="E70" s="9"/>
+      <c r="F70" s="13">
         <v>47.99</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C71" s="3">
         <v>100709</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E71" s="13"/>
-      <c r="F71" s="9">
+        <v>100</v>
+      </c>
+      <c r="E71" s="9"/>
+      <c r="F71" s="13">
         <v>35.99</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C72" s="3">
         <v>100737</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E72" s="13"/>
-      <c r="F72" s="9">
+        <v>101</v>
+      </c>
+      <c r="E72" s="9"/>
+      <c r="F72" s="13">
         <v>23.99</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C73" s="3">
         <v>289034</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E73" s="13"/>
-      <c r="F73" s="9">
+        <v>102</v>
+      </c>
+      <c r="E73" s="9"/>
+      <c r="F73" s="13">
         <v>7.99</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C74" s="3">
         <v>312579</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E74" s="13"/>
-      <c r="F74" s="9">
+        <v>103</v>
+      </c>
+      <c r="E74" s="9"/>
+      <c r="F74" s="13">
         <v>13.99</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C75" s="3">
         <v>273714</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E75" s="13"/>
-      <c r="F75" s="9">
+        <v>104</v>
+      </c>
+      <c r="E75" s="9"/>
+      <c r="F75" s="13">
         <v>7.99</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C76" s="6">
+      <c r="A76" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C76" s="3">
         <v>100780</v>
       </c>
-      <c r="D76" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E76" s="15"/>
-      <c r="F76" s="11">
+      <c r="D76" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E76" s="9"/>
+      <c r="F76" s="13">
         <v>2.99</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C77" s="3">
         <v>100789</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F77" s="9">
+        <v>106</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F77" s="13">
         <v>8.49</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C78" s="3">
         <v>101728</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E78" s="13"/>
-      <c r="F78" s="9">
+        <v>108</v>
+      </c>
+      <c r="E78" s="9"/>
+      <c r="F78" s="13">
         <v>12.99</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C79" s="3">
         <v>115724</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E79" s="13"/>
-      <c r="F79" s="9">
+        <v>109</v>
+      </c>
+      <c r="E79" s="9"/>
+      <c r="F79" s="13">
         <v>2.89</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C80" s="3">
         <v>259414</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E80" s="13"/>
-      <c r="F80" s="9">
+        <v>110</v>
+      </c>
+      <c r="E80" s="9"/>
+      <c r="F80" s="13">
         <v>2.19</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C81" s="6">
+      <c r="A81" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C81" s="3">
         <v>321107</v>
       </c>
-      <c r="D81" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E81" s="15"/>
-      <c r="F81" s="11">
+      <c r="D81" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E81" s="9"/>
+      <c r="F81" s="13">
         <v>1.99</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C82" s="3">
         <v>100876</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E82" s="13"/>
-      <c r="F82" s="9">
+        <v>112</v>
+      </c>
+      <c r="E82" s="9"/>
+      <c r="F82" s="13">
         <v>14.49</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C83" s="3">
         <v>119560</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E83" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="F83" s="9">
+        <v>113</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F83" s="13">
         <v>5.49</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C84" s="3">
         <v>106961</v>
       </c>
       <c r="D84" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F84" s="13">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C85" s="3">
+        <v>107640</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E84" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="F84" s="9">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C85" s="6">
-        <v>107640</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="E85" s="15"/>
-      <c r="F85" s="11">
+      <c r="E85" s="9"/>
+      <c r="F85" s="13">
         <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C86" s="3">
         <v>234316</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E86" s="13"/>
-      <c r="F86" s="9">
+        <v>119</v>
+      </c>
+      <c r="E86" s="9"/>
+      <c r="F86" s="13">
         <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C87" s="3">
         <v>100754</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E87" s="13"/>
-      <c r="F87" s="9">
+        <v>120</v>
+      </c>
+      <c r="E87" s="9"/>
+      <c r="F87" s="13">
         <v>23.99</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C88" s="3">
         <v>287208</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E88" s="13"/>
-      <c r="F88" s="9">
+        <v>121</v>
+      </c>
+      <c r="E88" s="9"/>
+      <c r="F88" s="13">
         <v>19.989999999999998</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C89" s="3">
         <v>100705</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E89" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="F89" s="9">
+        <v>123</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F89" s="13">
         <v>5.99</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C90" s="3">
         <v>142475</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E90" s="13"/>
-      <c r="F90" s="9">
+        <v>126</v>
+      </c>
+      <c r="E90" s="9"/>
+      <c r="F90" s="13">
         <v>3.19</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C91" s="3">
         <v>100642</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E91" s="13"/>
-      <c r="F91" s="9">
+        <v>127</v>
+      </c>
+      <c r="E91" s="9"/>
+      <c r="F91" s="13">
         <v>2.99</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C92" s="3">
         <v>274807</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E92" s="13"/>
-      <c r="F92" s="9">
+        <v>128</v>
+      </c>
+      <c r="E92" s="9"/>
+      <c r="F92" s="13">
         <v>2.89</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C93" s="3">
         <v>100632</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E93" s="13"/>
-      <c r="F93" s="9">
+        <v>129</v>
+      </c>
+      <c r="E93" s="9"/>
+      <c r="F93" s="13">
         <v>11.99</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C95" s="3">
-        <v>108686</v>
+        <v>105450</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E95" s="13"/>
-      <c r="F95" s="9">
-        <v>7.69</v>
+        <v>132</v>
+      </c>
+      <c r="E95" s="9"/>
+      <c r="F95" s="13">
+        <v>38.99</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C96" s="3">
+        <v>158997</v>
+      </c>
+      <c r="D96" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C96" s="3">
-        <v>104406</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E96" s="13"/>
-      <c r="F96" s="9">
-        <v>11.49</v>
+      <c r="E96" s="9"/>
+      <c r="F96" s="13">
+        <v>15.99</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C97" s="3">
+        <v>105461</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C97" s="3">
-        <v>104404</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E97" s="13"/>
-      <c r="F97" s="9">
-        <v>10.49</v>
+      <c r="E97" s="9"/>
+      <c r="F97" s="13">
+        <v>27.99</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C98" s="3">
-        <v>104403</v>
+        <v>105457</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E98" s="13"/>
-      <c r="F98" s="9">
-        <v>10.19</v>
+        <v>135</v>
+      </c>
+      <c r="E98" s="9"/>
+      <c r="F98" s="13">
+        <v>28.99</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C99" s="3">
-        <v>104410</v>
+        <v>105456</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E99" s="13"/>
-      <c r="F99" s="9">
-        <v>9.49</v>
+        <v>136</v>
+      </c>
+      <c r="E99" s="9"/>
+      <c r="F99" s="13">
+        <v>25.99</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C100" s="3">
-        <v>102287</v>
+        <v>105468</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E100" s="13"/>
-      <c r="F100" s="9">
-        <v>4.3899999999999997</v>
+        <v>137</v>
+      </c>
+      <c r="E100" s="9"/>
+      <c r="F100" s="13">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C101" s="3">
-        <v>117100</v>
+        <v>105458</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="E101" s="13"/>
-      <c r="F101" s="9">
-        <v>12.99</v>
+        <v>138</v>
+      </c>
+      <c r="E101" s="9"/>
+      <c r="F101" s="13">
+        <v>14.99</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="C102" s="3">
-        <v>286325</v>
+        <v>105451</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E102" s="13"/>
-      <c r="F102" s="9">
-        <v>22.99</v>
+        <v>139</v>
+      </c>
+      <c r="E102" s="9"/>
+      <c r="F102" s="13">
+        <v>38.99</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="C103" s="3">
-        <v>264452</v>
+        <v>105471</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E103" s="13"/>
-      <c r="F103" s="9">
-        <v>5.99</v>
+        <v>140</v>
+      </c>
+      <c r="E103" s="9"/>
+      <c r="F103" s="13">
+        <v>20.59</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="C104" s="3">
-        <v>247800</v>
+        <v>105435</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E104" s="13"/>
-      <c r="F104" s="9">
-        <v>6.29</v>
+        <v>141</v>
+      </c>
+      <c r="E104" s="9"/>
+      <c r="F104" s="13">
+        <v>33.99</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="C105" s="3">
-        <v>247799</v>
+        <v>298422</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="E105" s="13"/>
-      <c r="F105" s="9">
-        <v>6.29</v>
+        <v>142</v>
+      </c>
+      <c r="E105" s="9"/>
+      <c r="F105" s="13">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C106" s="3">
-        <v>242930</v>
+        <v>106053</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="E106" s="13"/>
-      <c r="F106" s="9">
-        <v>7.19</v>
+        <v>144</v>
+      </c>
+      <c r="E106" s="9"/>
+      <c r="F106" s="13">
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C107" s="3">
-        <v>239446</v>
+        <v>105062</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E107" s="13"/>
-      <c r="F107" s="9">
-        <f>12*3.19</f>
-        <v>38.28</v>
+        <v>145</v>
+      </c>
+      <c r="E107" s="9"/>
+      <c r="F107" s="13">
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C108" s="3">
-        <v>168712</v>
+        <v>106008</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E108" s="13"/>
-      <c r="F108" s="9">
-        <f>15*3.39</f>
-        <v>50.85</v>
+        <v>146</v>
+      </c>
+      <c r="E108" s="9"/>
+      <c r="F108" s="13">
+        <v>13.99</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C109" s="3">
-        <v>170451</v>
+        <v>258810</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E109" s="13"/>
-      <c r="F109" s="9">
-        <f>15*3.29</f>
-        <v>49.35</v>
+        <v>147</v>
+      </c>
+      <c r="E109" s="9"/>
+      <c r="F109" s="13">
+        <v>14.99</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B110" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C110" s="3">
+        <v>305039</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E110" s="9"/>
+      <c r="F110" s="13">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C110" s="3">
+      <c r="B112" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C112" s="3">
+        <v>108686</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E112" s="9"/>
+      <c r="F112" s="13">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C113" s="3">
+        <v>104406</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E113" s="9"/>
+      <c r="F113" s="13">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C114" s="3">
+        <v>104404</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E114" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="F114" s="13">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C115" s="3">
+        <v>104410</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E115" s="9"/>
+      <c r="F115" s="13">
+        <v>8.89</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C116" s="3">
+        <v>117100</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E116" s="9"/>
+      <c r="F116" s="13">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C117" s="3">
+        <v>286325</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E117" s="9"/>
+      <c r="F117" s="13">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C118" s="3">
+        <v>264452</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E118" s="9"/>
+      <c r="F118" s="13">
+        <v>5.89</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C119" s="3">
+        <v>247800</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E119" s="9"/>
+      <c r="F119" s="13">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C120" s="3">
+        <v>247799</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E120" s="9"/>
+      <c r="F120" s="13">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C121" s="3">
+        <v>242930</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E121" s="9"/>
+      <c r="F121" s="13">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C122" s="3">
+        <v>239446</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E122" s="9"/>
+      <c r="F122" s="13">
+        <f>12*3.05</f>
+        <v>36.599999999999994</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C123" s="3">
+        <v>168712</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E123" s="9"/>
+      <c r="F123" s="13">
+        <f>15*3.25</f>
+        <v>48.75</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C124" s="3">
+        <v>170451</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E124" s="9"/>
+      <c r="F124" s="13">
+        <f>15*3.09</f>
+        <v>46.349999999999994</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C125" s="3">
         <v>108423</v>
       </c>
-      <c r="D110" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E110" s="13"/>
-      <c r="F110" s="9">
-        <f>6*7.19</f>
-        <v>43.14</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B111" s="2" t="s">
+      <c r="D125" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E125" s="9"/>
+      <c r="F125" s="13">
+        <f>6*6.99</f>
+        <v>41.94</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C111" s="3">
+      <c r="B126" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C126" s="3">
         <v>265727</v>
       </c>
-      <c r="D111" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E111" s="13"/>
-      <c r="F111" s="9">
+      <c r="D126" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E126" s="9"/>
+      <c r="F126" s="13">
         <f>8*4.49</f>
         <v>35.92</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C112" s="3">
-        <v>324556</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E112" s="13"/>
-      <c r="F112" s="9">
-        <f>15*3.09</f>
-        <v>46.349999999999994</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C113" s="3">
-        <v>236674</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E113" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="F113" s="9">
-        <v>42.99</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C114" s="3">
-        <v>293188</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E114" s="13"/>
-      <c r="F114" s="9">
-        <v>7.19</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C115" s="3">
-        <v>102085</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E115" s="13"/>
-      <c r="F115" s="9">
-        <v>13.49</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C116" s="3">
-        <v>215568</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="E116" s="13"/>
-      <c r="F116" s="9">
-        <v>39.99</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C117" s="3">
-        <v>301843</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E117" s="13"/>
-      <c r="F117" s="9">
-        <v>74.989999999999995</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C118" s="3">
-        <v>206930</v>
-      </c>
-      <c r="D118" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="E118" s="13"/>
-      <c r="F118" s="9">
-        <v>148.99</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C119" s="3">
-        <v>123548</v>
-      </c>
-      <c r="D119" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="E119" s="13"/>
-      <c r="F119" s="9">
-        <v>134.99</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C120" s="3">
-        <v>102077</v>
-      </c>
-      <c r="D120" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="E120" s="13"/>
-      <c r="F120" s="9">
-        <v>189.99</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C121" s="3">
-        <v>109729</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="E121" s="13"/>
-      <c r="F121" s="9">
-        <v>109.99</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C122" s="3">
-        <v>295198</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E122" s="13"/>
-      <c r="F122" s="9">
-        <v>11.69</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C123" s="3">
-        <v>102036</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E123" s="13"/>
-      <c r="F123" s="9">
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C124" s="3">
-        <v>139964</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="E124" s="13"/>
-      <c r="F124" s="9">
-        <v>28.99</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C126" s="3">
-        <v>104931</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="E126" s="13"/>
-      <c r="F126" s="9">
-        <v>6.99</v>
-      </c>
-    </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C127" s="3">
+        <v>324556</v>
+      </c>
+      <c r="D127" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C127" s="3">
-        <v>104944</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="E127" s="13"/>
-      <c r="F127" s="9">
-        <v>12.99</v>
+      <c r="E127" s="9"/>
+      <c r="F127" s="13">
+        <f>15*2.99</f>
+        <v>44.85</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C128" s="3">
-        <v>105010</v>
+        <v>236674</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="E128" s="13"/>
-      <c r="F128" s="9">
-        <v>2.99</v>
+        <v>174</v>
+      </c>
+      <c r="E128" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F128" s="13">
+        <v>40.99</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="B129" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C129" s="3">
+        <v>293188</v>
+      </c>
+      <c r="D129" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C129" s="3">
-        <v>105001</v>
-      </c>
-      <c r="D129" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="E129" s="13"/>
-      <c r="F129" s="9">
-        <v>2.99</v>
+      <c r="E129" s="9"/>
+      <c r="F129" s="13">
+        <v>6.99</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C130" s="3">
-        <v>104862</v>
+        <v>102085</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E130" s="13"/>
-      <c r="F130" s="9">
-        <v>2.99</v>
+        <v>177</v>
+      </c>
+      <c r="E130" s="9"/>
+      <c r="F130" s="13">
+        <v>12.59</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C131" s="3">
-        <v>104961</v>
+        <v>215568</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="E131" s="13"/>
-      <c r="F131" s="9">
-        <v>4.99</v>
+        <v>178</v>
+      </c>
+      <c r="E131" s="9"/>
+      <c r="F131" s="13">
+        <v>35.99</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C132" s="3">
-        <v>104919</v>
+        <v>301843</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="E132" s="13"/>
-      <c r="F132" s="9">
-        <v>2.59</v>
+        <v>179</v>
+      </c>
+      <c r="E132" s="9"/>
+      <c r="F132" s="13">
+        <v>65.989999999999995</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C133" s="3">
-        <v>104992</v>
+        <v>206930</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="E133" s="13"/>
-      <c r="F133" s="9">
-        <v>2.99</v>
+        <v>180</v>
+      </c>
+      <c r="E133" s="9"/>
+      <c r="F133" s="13">
+        <v>142.99</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C134" s="3">
+        <v>123548</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E134" s="9"/>
+      <c r="F134" s="13">
+        <v>125.99</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="C135" s="3">
-        <v>328966</v>
+        <v>102077</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="E135" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="F135" s="9">
-        <v>17.989999999999998</v>
+        <v>182</v>
+      </c>
+      <c r="E135" s="9"/>
+      <c r="F135" s="13">
+        <v>179.99</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C136" s="3">
+        <v>109729</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E136" s="9"/>
+      <c r="F136" s="13">
+        <v>95.99</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C137" s="3">
-        <v>100426</v>
+        <v>295198</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E137" s="13"/>
-      <c r="F137" s="9">
-        <v>3.69</v>
+        <v>185</v>
+      </c>
+      <c r="E137" s="9"/>
+      <c r="F137" s="13">
+        <v>10.99</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C138" s="3">
+        <v>102036</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E138" s="9"/>
+      <c r="F138" s="13">
+        <v>23.59</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C140" s="6">
+        <v>324330</v>
+      </c>
+      <c r="D140" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="E140" s="11"/>
+      <c r="F140" s="15">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C141" s="6">
+        <v>324328</v>
+      </c>
+      <c r="D141" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C138" s="3">
-        <v>100431</v>
-      </c>
-      <c r="D138" s="4" t="s">
+      <c r="E141" s="11"/>
+      <c r="F141" s="15">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C142" s="6">
+        <v>335127</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E142" s="11"/>
+      <c r="F142" s="15">
+        <v>63.2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C143" s="6">
+        <v>324334</v>
+      </c>
+      <c r="D143" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="E138" s="13"/>
-      <c r="F138" s="9">
-        <v>7.19</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B139" s="2" t="s">
+      <c r="E143" s="11"/>
+      <c r="F143" s="15">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C144" s="6">
+        <v>324327</v>
+      </c>
+      <c r="D144" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="C139" s="3">
-        <v>133368</v>
-      </c>
-      <c r="D139" s="4" t="s">
+      <c r="E144" s="11"/>
+      <c r="F144" s="15">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C145" s="6">
+        <v>231569</v>
+      </c>
+      <c r="D145" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="E139" s="13"/>
-      <c r="F139" s="9">
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C140" s="3">
-        <v>107393</v>
-      </c>
-      <c r="D140" s="4" t="s">
+      <c r="E145" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="E140" s="13" t="s">
+      <c r="F145" s="15">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C146" s="6">
+        <v>260718</v>
+      </c>
+      <c r="D146" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="F140" s="9">
-        <v>11.49</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A141" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B141" s="2" t="s">
+      <c r="E146" s="11"/>
+      <c r="F146" s="15">
+        <v>76.8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C147" s="6">
+        <v>328788</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E147" s="11"/>
+      <c r="F147" s="15">
+        <v>65.599999999999994</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C148" s="6">
+        <v>327330</v>
+      </c>
+      <c r="D148" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="C141" s="3">
-        <v>100279</v>
-      </c>
-      <c r="D141" s="4" t="s">
+      <c r="E148" s="11"/>
+      <c r="F148" s="15">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C149" s="6">
+        <v>231570</v>
+      </c>
+      <c r="D149" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="E141" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="F141" s="9">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C142" s="3">
-        <v>142863</v>
-      </c>
-      <c r="D142" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E142" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="F142" s="9">
-        <v>12.69</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A143" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C143" s="3">
-        <v>207586</v>
-      </c>
-      <c r="D143" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="E143" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="F143" s="9">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A144" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C144" s="3">
-        <v>100391</v>
-      </c>
-      <c r="D144" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="E144" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="F144" s="9">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C145" s="3">
-        <v>100511</v>
-      </c>
-      <c r="D145" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="E145" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="F145" s="9">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C146" s="3">
-        <v>156422</v>
-      </c>
-      <c r="D146" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E146" s="13"/>
-      <c r="F146" s="9">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A147" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C147" s="3">
-        <v>290791</v>
-      </c>
-      <c r="D147" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="E147" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="F147" s="9">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C148" s="3">
-        <v>326954</v>
-      </c>
-      <c r="D148" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="E148" s="13"/>
-      <c r="F148" s="9">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C149" s="3">
-        <v>257710</v>
-      </c>
-      <c r="D149" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="E149" s="13"/>
-      <c r="F149" s="9">
-        <v>11.99</v>
+      <c r="E149" s="11"/>
+      <c r="F149" s="15">
+        <v>76</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>213</v>
+        <v>25</v>
       </c>
       <c r="C150" s="6">
-        <v>261980</v>
+        <v>293779</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="E150" s="15"/>
-      <c r="F150" s="11">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C151" s="3">
-        <v>263649</v>
-      </c>
-      <c r="D151" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="E151" s="13"/>
-      <c r="F151" s="9">
-        <v>17.989999999999998</v>
+        <v>198</v>
+      </c>
+      <c r="E150" s="11"/>
+      <c r="F150" s="15">
+        <v>66.400000000000006</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A151" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C151" s="6">
+        <v>324335</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E151" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="F151" s="15">
+        <v>45.6</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C152" s="3">
-        <v>228234</v>
-      </c>
-      <c r="D152" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="E152" s="13"/>
-      <c r="F152" s="9">
-        <v>13.99</v>
+      <c r="A152" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C152" s="6">
+        <v>324329</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E152" s="11"/>
+      <c r="F152" s="15">
+        <v>42.4</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C153" s="3">
-        <v>286199</v>
-      </c>
-      <c r="D153" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="E153" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="F153" s="9">
-        <v>10.99</v>
+      <c r="A153" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C153" s="6">
+        <v>259776</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E153" s="11"/>
+      <c r="F153" s="15">
+        <v>84.8</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A154" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C154" s="3">
-        <v>150356</v>
-      </c>
-      <c r="D154" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E154" s="13"/>
-      <c r="F154" s="9">
-        <v>46.99</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C155" s="3">
-        <v>100373</v>
-      </c>
-      <c r="D155" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E155" s="13"/>
-      <c r="F155" s="9">
-        <v>23.99</v>
+      <c r="A154" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C154" s="6">
+        <v>324331</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="E154" s="11"/>
+      <c r="F154" s="15">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C156" s="3">
+        <v>105023</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E156" s="9"/>
+      <c r="F156" s="13">
+        <v>5.59</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="C157" s="3">
-        <v>252582</v>
+        <v>104931</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E157" s="13"/>
-      <c r="F157" s="9">
-        <v>38.99</v>
+        <v>207</v>
+      </c>
+      <c r="E157" s="9"/>
+      <c r="F157" s="13">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C158" s="3">
+        <v>105010</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E158" s="9"/>
+      <c r="F158" s="13">
+        <v>4.49</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="C159" s="3">
-        <v>105838</v>
+        <v>105001</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E159" s="13"/>
-      <c r="F159" s="9">
-        <v>10.99</v>
+        <v>210</v>
+      </c>
+      <c r="E159" s="9"/>
+      <c r="F159" s="13">
+        <v>3.79</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="C160" s="3">
-        <v>105840</v>
+        <v>104862</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="E160" s="13"/>
-      <c r="F160" s="9">
-        <v>15.99</v>
+        <v>211</v>
+      </c>
+      <c r="E160" s="9"/>
+      <c r="F160" s="13">
+        <v>3.49</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="C161" s="3">
-        <v>109597</v>
+        <v>104961</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="E161" s="13"/>
-      <c r="F161" s="9">
-        <v>17.989999999999998</v>
+        <v>212</v>
+      </c>
+      <c r="E161" s="9"/>
+      <c r="F161" s="13">
+        <v>4.99</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="C162" s="3">
-        <v>119927</v>
+        <v>104919</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="E162" s="13"/>
-      <c r="F162" s="9">
-        <v>9.99</v>
+        <v>214</v>
+      </c>
+      <c r="E162" s="9"/>
+      <c r="F162" s="13">
+        <v>1.99</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="C163" s="3">
-        <v>105788</v>
+        <v>104992</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="E163" s="13"/>
-      <c r="F163" s="9">
-        <v>28.99</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C164" s="3">
-        <v>329843</v>
-      </c>
-      <c r="D164" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="E164" s="13"/>
-      <c r="F164" s="9">
-        <v>19.989999999999998</v>
+        <v>216</v>
+      </c>
+      <c r="E163" s="9"/>
+      <c r="F163" s="13">
+        <v>2.89</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="C165" s="3">
-        <v>228422</v>
+        <v>100426</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="E165" s="13"/>
-      <c r="F165" s="9">
-        <v>17.989999999999998</v>
+        <v>219</v>
+      </c>
+      <c r="E165" s="9"/>
+      <c r="F165" s="13">
+        <v>3.69</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="C166" s="3">
-        <v>189031</v>
+        <v>100431</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="E166" s="13"/>
-      <c r="F166" s="9">
-        <v>17.989999999999998</v>
+        <v>220</v>
+      </c>
+      <c r="E166" s="9"/>
+      <c r="F166" s="13">
+        <v>7.19</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C167" s="3">
-        <v>105765</v>
+        <v>133368</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="E167" s="13"/>
-      <c r="F167" s="9">
-        <v>9.99</v>
+        <v>222</v>
+      </c>
+      <c r="E167" s="9"/>
+      <c r="F167" s="13">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C168" s="3">
-        <v>129516</v>
+        <v>107393</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="E168" s="13"/>
-      <c r="F168" s="9">
-        <v>28.99</v>
+        <v>223</v>
+      </c>
+      <c r="E168" s="9"/>
+      <c r="F168" s="13">
+        <v>11.49</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B169" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B169" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="C169" s="3">
-        <v>132881</v>
+        <v>100279</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="E169" s="13"/>
-      <c r="F169" s="9">
-        <v>8.99</v>
+        <v>225</v>
+      </c>
+      <c r="E169" s="9"/>
+      <c r="F169" s="13">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C170" s="3">
+        <v>142863</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E170" s="9"/>
+      <c r="F170" s="13">
+        <v>12.69</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="C171" s="3">
-        <v>268136</v>
+        <v>207586</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="E171" s="13"/>
-      <c r="F171" s="9">
-        <v>13.99</v>
+        <v>228</v>
+      </c>
+      <c r="E171" s="9"/>
+      <c r="F171" s="13">
+        <v>1.69</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="C172" s="3">
-        <v>276943</v>
+        <v>100391</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="E172" s="13"/>
-      <c r="F172" s="9">
-        <v>14.49</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+      <c r="E172" s="9"/>
+      <c r="F172" s="13">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>86</v>
+        <v>230</v>
       </c>
       <c r="C173" s="3">
-        <v>246975</v>
+        <v>100511</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="E173" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="F173" s="9">
-        <v>18.989999999999998</v>
+        <v>231</v>
+      </c>
+      <c r="E173" s="9"/>
+      <c r="F173" s="13">
+        <v>3.89</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C174" s="3">
-        <v>222974</v>
+        <v>156422</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="E174" s="13"/>
-      <c r="F174" s="9">
-        <v>7.49</v>
+        <v>233</v>
+      </c>
+      <c r="E174" s="9"/>
+      <c r="F174" s="13">
+        <v>5.99</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C175" s="3">
-        <v>332779</v>
+        <v>290791</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="E175" s="13"/>
-      <c r="F175" s="9">
-        <v>15.3</v>
+        <v>234</v>
+      </c>
+      <c r="E175" s="9"/>
+      <c r="F175" s="13">
+        <v>12.99</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="C176" s="3">
-        <v>156502</v>
+        <v>326954</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="E176" s="13"/>
-      <c r="F176" s="9">
-        <v>40.5</v>
+        <v>236</v>
+      </c>
+      <c r="E176" s="9"/>
+      <c r="F176" s="13">
+        <v>8.99</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="C177" s="3">
-        <v>155246</v>
+        <v>257710</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="E177" s="13"/>
-      <c r="F177" s="9">
-        <v>13.5</v>
+        <v>237</v>
+      </c>
+      <c r="E177" s="9"/>
+      <c r="F177" s="13">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C178" s="3">
+        <v>261980</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E178" s="9"/>
+      <c r="F178" s="13">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C179" s="3">
+        <v>263649</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E179" s="9"/>
+      <c r="F179" s="13">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C180" s="3">
+        <v>228234</v>
+      </c>
+      <c r="D180" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="B179" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C179" s="3">
-        <v>215182</v>
-      </c>
-      <c r="D179" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="E179" s="13"/>
-      <c r="F179" s="9">
-        <v>19.989999999999998</v>
+      <c r="E180" s="9"/>
+      <c r="F180" s="13">
+        <v>13.99</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C181" s="3">
-        <v>108785</v>
+        <v>286199</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="E181" s="13"/>
-      <c r="F181" s="9">
-        <v>16.989999999999998</v>
+        <v>241</v>
+      </c>
+      <c r="E181" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="F181" s="13">
+        <v>10.99</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C182" s="3">
-        <v>108774</v>
+        <v>150356</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="E182" s="13"/>
-      <c r="F182" s="9">
-        <v>19.989999999999998</v>
+        <v>243</v>
+      </c>
+      <c r="E182" s="9"/>
+      <c r="F182" s="13">
+        <v>46.99</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C183" s="3">
-        <v>227259</v>
+        <v>100373</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="E183" s="13"/>
-      <c r="F183" s="9">
-        <v>6.79</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C184" s="3">
-        <v>138538</v>
-      </c>
-      <c r="D184" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="E184" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="F184" s="9">
-        <v>8.19</v>
+        <v>245</v>
+      </c>
+      <c r="E183" s="9"/>
+      <c r="F183" s="13">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C185" s="3">
+        <v>133469</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E185" s="9"/>
+      <c r="F185" s="13">
+        <v>4.99</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>25</v>
+        <v>248</v>
       </c>
       <c r="C186" s="3">
-        <v>242795</v>
+        <v>108410</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="E186" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="F186" s="9">
-        <v>25.99</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C187" s="3">
-        <v>289007</v>
-      </c>
-      <c r="D187" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="E187" s="13"/>
-      <c r="F187" s="9">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+      <c r="E186" s="9"/>
+      <c r="F186" s="13">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>25</v>
+        <v>251</v>
       </c>
       <c r="C188" s="3">
-        <v>138139</v>
+        <v>237712</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="E188" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="F188" s="9">
-        <v>9.99</v>
+        <v>252</v>
+      </c>
+      <c r="E188" s="9"/>
+      <c r="F188" s="13">
+        <v>32.99</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>25</v>
+        <v>251</v>
       </c>
       <c r="C189" s="3">
-        <v>156523</v>
+        <v>150899</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="E189" s="13"/>
-      <c r="F189" s="9">
-        <v>16</v>
+        <v>253</v>
+      </c>
+      <c r="E189" s="9"/>
+      <c r="F189" s="13">
+        <v>69.989999999999995</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>25</v>
+        <v>251</v>
       </c>
       <c r="C190" s="3">
-        <v>297570</v>
+        <v>324722</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="E190" s="13"/>
-      <c r="F190" s="9">
-        <v>15.99</v>
+        <v>254</v>
+      </c>
+      <c r="E190" s="9"/>
+      <c r="F190" s="13">
+        <v>64.989999999999995</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>25</v>
+        <v>251</v>
       </c>
       <c r="C191" s="3">
-        <v>297599</v>
+        <v>105921</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="E191" s="13"/>
-      <c r="F191" s="9">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A192" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C192" s="3">
-        <v>277148</v>
-      </c>
-      <c r="D192" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="E192" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="F192" s="9">
-        <v>15.99</v>
+        <v>255</v>
+      </c>
+      <c r="E191" s="9"/>
+      <c r="F191" s="13">
+        <v>7.69</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C193" s="3">
+        <v>252582</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E193" s="9"/>
+      <c r="F193" s="13">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B195" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B193" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C193" s="3">
-        <v>255029</v>
-      </c>
-      <c r="D193" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="E193" s="13"/>
-      <c r="F193" s="9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A194" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C194" s="3">
-        <v>162945</v>
-      </c>
-      <c r="D194" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="E194" s="13"/>
-      <c r="F194" s="9">
-        <v>17.600000000000001</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A195" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="C195" s="3">
-        <v>161653</v>
+        <v>105838</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="E195" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="F195" s="9">
-        <v>7.99</v>
+        <v>260</v>
+      </c>
+      <c r="E195" s="9"/>
+      <c r="F195" s="13">
+        <v>10.99</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B196" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B196" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="C196" s="3">
-        <v>215573</v>
+        <v>105840</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="E196" s="13"/>
-      <c r="F196" s="9">
-        <v>12</v>
+        <v>261</v>
+      </c>
+      <c r="E196" s="9"/>
+      <c r="F196" s="13">
+        <v>15.99</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B197" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B197" s="2" t="s">
-        <v>275</v>
-      </c>
       <c r="C197" s="3">
-        <v>182034</v>
+        <v>109597</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="E197" s="13"/>
-      <c r="F197" s="9">
-        <v>14.99</v>
+        <v>262</v>
+      </c>
+      <c r="E197" s="9"/>
+      <c r="F197" s="13">
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B198" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B198" s="2" t="s">
-        <v>275</v>
-      </c>
       <c r="C198" s="3">
-        <v>314034</v>
+        <v>119927</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="E198" s="13"/>
-      <c r="F198" s="9">
-        <v>10.99</v>
+        <v>263</v>
+      </c>
+      <c r="E198" s="9"/>
+      <c r="F198" s="13">
+        <v>9.99</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>275</v>
+        <v>148</v>
       </c>
       <c r="C199" s="3">
-        <v>313968</v>
+        <v>105788</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="E199" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="F199" s="9">
-        <v>10.99</v>
+        <v>264</v>
+      </c>
+      <c r="E199" s="9"/>
+      <c r="F199" s="13">
+        <v>28.99</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="B200" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C200" s="6">
-        <v>208281</v>
-      </c>
-      <c r="D200" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="E200" s="15"/>
-      <c r="F200" s="11">
-        <v>6.99</v>
+      <c r="A200" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C200" s="3">
+        <v>329843</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="E200" s="9"/>
+      <c r="F200" s="13">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>281</v>
+        <v>148</v>
       </c>
       <c r="C201" s="3">
-        <v>258213</v>
+        <v>228422</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="E201" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="F201" s="9">
-        <v>28.99</v>
+        <v>266</v>
+      </c>
+      <c r="E201" s="9"/>
+      <c r="F201" s="13">
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>281</v>
+        <v>148</v>
       </c>
       <c r="C202" s="3">
-        <v>229916</v>
+        <v>189031</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="E202" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="F202" s="9">
-        <v>49.99</v>
+        <v>267</v>
+      </c>
+      <c r="E202" s="9"/>
+      <c r="F202" s="13">
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>286</v>
+        <v>148</v>
       </c>
       <c r="C203" s="3">
-        <v>199322</v>
+        <v>105765</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="E203" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="F203" s="9">
+        <v>268</v>
+      </c>
+      <c r="E203" s="9"/>
+      <c r="F203" s="13">
         <v>9.99</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>289</v>
+        <v>148</v>
       </c>
       <c r="C204" s="3">
-        <v>227236</v>
+        <v>129516</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="E204" s="13"/>
-      <c r="F204" s="9">
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+      <c r="E204" s="9"/>
+      <c r="F204" s="13">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>289</v>
+        <v>148</v>
       </c>
       <c r="C205" s="3">
-        <v>109064</v>
+        <v>132881</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="E205" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="F205" s="9">
+        <v>270</v>
+      </c>
+      <c r="E205" s="9"/>
+      <c r="F205" s="13">
         <v>8.99</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C206" s="3">
-        <v>256740</v>
-      </c>
-      <c r="D206" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="E206" s="13"/>
-      <c r="F206" s="9">
-        <v>9.6</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="C207" s="3">
-        <v>242760</v>
+        <v>268136</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="E207" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="F207" s="9">
-        <v>8</v>
+        <v>273</v>
+      </c>
+      <c r="E207" s="9"/>
+      <c r="F207" s="13">
+        <v>13.99</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="C208" s="3">
-        <v>242759</v>
+        <v>276943</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="E208" s="13"/>
-      <c r="F208" s="9">
-        <v>7.59</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A209" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="B209" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C209" s="6">
-        <v>103700</v>
-      </c>
-      <c r="D209" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="E209" s="15" t="s">
-        <v>299</v>
-      </c>
-      <c r="F209" s="11">
-        <v>9.99</v>
+        <v>275</v>
+      </c>
+      <c r="E208" s="9"/>
+      <c r="F208" s="13">
+        <v>14.49</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C209" s="3">
+        <v>246975</v>
+      </c>
+      <c r="D209" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E209" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="F209" s="13">
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A210" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="B210" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="C210" s="6">
-        <v>265970</v>
-      </c>
-      <c r="D210" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="E210" s="15"/>
-      <c r="F210" s="11">
-        <v>25.99</v>
+      <c r="A210" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C210" s="3">
+        <v>222974</v>
+      </c>
+      <c r="D210" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="E210" s="9"/>
+      <c r="F210" s="13">
+        <v>7.49</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A211" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="B211" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="C211" s="6">
-        <v>104371</v>
-      </c>
-      <c r="D211" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="E211" s="15"/>
-      <c r="F211" s="11">
-        <v>9.99</v>
+      <c r="A211" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C211" s="3">
+        <v>332779</v>
+      </c>
+      <c r="D211" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="E211" s="9"/>
+      <c r="F211" s="13">
+        <v>15.3</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>303</v>
+        <v>257</v>
       </c>
       <c r="C212" s="3">
-        <v>108866</v>
+        <v>155246</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="E212" s="13"/>
-      <c r="F212" s="9">
-        <v>3.76</v>
+        <v>280</v>
+      </c>
+      <c r="E212" s="9"/>
+      <c r="F212" s="13">
+        <v>13.5</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C213" s="3">
+        <v>156502</v>
+      </c>
+      <c r="D213" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E213" s="9"/>
+      <c r="F213" s="13">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C215" s="3">
+        <v>215182</v>
+      </c>
+      <c r="D215" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="E215" s="9"/>
+      <c r="F215" s="13">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B217" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B213" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C213" s="3">
-        <v>187000</v>
-      </c>
-      <c r="D213" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="E213" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="F213" s="9">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A215" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C215" s="3">
-        <v>100886</v>
-      </c>
-      <c r="D215" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="E215" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="F215" s="9">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A216" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C216" s="3">
-        <v>237472</v>
-      </c>
-      <c r="D216" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="E216" s="13"/>
-      <c r="F216" s="9">
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" ht="48" x14ac:dyDescent="0.25">
-      <c r="A217" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>311</v>
-      </c>
       <c r="C217" s="3">
-        <v>108412</v>
+        <v>108785</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="E217" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="F217" s="9">
-        <v>1.99</v>
+        <v>284</v>
+      </c>
+      <c r="E217" s="9"/>
+      <c r="F217" s="13">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C218" s="3">
+        <v>108774</v>
+      </c>
+      <c r="D218" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="E218" s="9"/>
+      <c r="F218" s="13">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>315</v>
+        <v>271</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>192</v>
+        <v>148</v>
       </c>
       <c r="C219" s="3">
-        <v>285689</v>
+        <v>227259</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="E219" s="13"/>
-      <c r="F219" s="9">
-        <v>10.99</v>
+        <v>286</v>
+      </c>
+      <c r="E219" s="9"/>
+      <c r="F219" s="13">
+        <v>6.79</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>315</v>
+        <v>271</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>196</v>
+        <v>287</v>
       </c>
       <c r="C220" s="3">
-        <v>186012</v>
+        <v>138538</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="E220" s="13"/>
-      <c r="F220" s="9">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A221" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C221" s="3">
-        <v>123791</v>
-      </c>
-      <c r="D221" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E221" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="F221" s="9">
-        <v>9.99</v>
+        <v>288</v>
+      </c>
+      <c r="E220" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="F220" s="13">
+        <v>8.19</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>315</v>
+        <v>290</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>320</v>
+        <v>25</v>
       </c>
       <c r="C222" s="3">
-        <v>200131</v>
+        <v>242795</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="E222" s="13"/>
-      <c r="F222" s="9">
-        <v>36.99</v>
+        <v>291</v>
+      </c>
+      <c r="E222" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="F222" s="13">
+        <v>25.99</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C223" s="3">
+        <v>289007</v>
+      </c>
+      <c r="D223" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E223" s="9"/>
+      <c r="F223" s="13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C224" s="3">
+        <v>138139</v>
+      </c>
+      <c r="D224" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="E224" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="F224" s="13">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C225" s="3">
+        <v>156523</v>
+      </c>
+      <c r="D225" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E225" s="9"/>
+      <c r="F225" s="13">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A226" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C226" s="3">
+        <v>277148</v>
+      </c>
+      <c r="D226" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E226" s="9"/>
+      <c r="F226" s="13">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A227" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C227" s="6">
+        <v>297570</v>
+      </c>
+      <c r="D227" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E227" s="11"/>
+      <c r="F227" s="15">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A228" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C228" s="3">
+        <v>297599</v>
+      </c>
+      <c r="D228" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="E228" s="9"/>
+      <c r="F228" s="13">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A229" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C229" s="3">
+        <v>161653</v>
+      </c>
+      <c r="D229" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E229" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="F229" s="13">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A230" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C230" s="3">
+        <v>215573</v>
+      </c>
+      <c r="D230" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E230" s="9"/>
+      <c r="F230" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A231" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C231" s="3">
+        <v>182034</v>
+      </c>
+      <c r="D231" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="E231" s="9"/>
+      <c r="F231" s="13">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A232" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C232" s="3">
+        <v>314034</v>
+      </c>
+      <c r="D232" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="E232" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="F232" s="13">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C233" s="3">
+        <v>208281</v>
+      </c>
+      <c r="D233" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="E233" s="9"/>
+      <c r="F233" s="13">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A234" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C234" s="3">
+        <v>258213</v>
+      </c>
+      <c r="D234" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E234" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="F234" s="13">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C235" s="3">
+        <v>229916</v>
+      </c>
+      <c r="D235" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="E235" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="F235" s="13">
+        <v>49.99</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A236" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C236" s="3">
+        <v>199322</v>
+      </c>
+      <c r="D236" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="E236" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="B223" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C223" s="3">
+      <c r="F236" s="13">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A237" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C237" s="3">
+        <v>109064</v>
+      </c>
+      <c r="D237" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E237" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="F237" s="13">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A238" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C238" s="3">
+        <v>256740</v>
+      </c>
+      <c r="D238" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E238" s="9"/>
+      <c r="F238" s="13">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A239" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C239" s="3">
+        <v>242760</v>
+      </c>
+      <c r="D239" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E239" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="F239" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C240" s="3">
+        <v>242759</v>
+      </c>
+      <c r="D240" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="E240" s="9"/>
+      <c r="F240" s="13">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C241" s="3">
+        <v>103700</v>
+      </c>
+      <c r="D241" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="E241" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="F241" s="13">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A242" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C242" s="3">
+        <v>265970</v>
+      </c>
+      <c r="D242" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E242" s="9"/>
+      <c r="F242" s="13">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C243" s="3">
+        <v>104371</v>
+      </c>
+      <c r="D243" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="E243" s="9"/>
+      <c r="F243" s="13">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A244" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C244" s="3">
+        <v>268023</v>
+      </c>
+      <c r="D244" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="E244" s="9"/>
+      <c r="F244" s="13">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A245" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C245" s="3">
+        <v>187000</v>
+      </c>
+      <c r="D245" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E245" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="F245" s="13">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A247" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C247" s="3">
+        <v>100886</v>
+      </c>
+      <c r="D247" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="E247" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="F247" s="13">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C248" s="3">
+        <v>108412</v>
+      </c>
+      <c r="D248" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="E248" s="9"/>
+      <c r="F248" s="13">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A250" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C250" s="3">
+        <v>285689</v>
+      </c>
+      <c r="D250" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="E250" s="9"/>
+      <c r="F250" s="13">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A251" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C251" s="3">
+        <v>186012</v>
+      </c>
+      <c r="D251" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="E251" s="9"/>
+      <c r="F251" s="13">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A252" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C252" s="3">
+        <v>123791</v>
+      </c>
+      <c r="D252" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="E252" s="9"/>
+      <c r="F252" s="13">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A253" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C253" s="3">
+        <v>200131</v>
+      </c>
+      <c r="D253" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="E253" s="9"/>
+      <c r="F253" s="13">
+        <v>36.99</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A254" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C254" s="3">
         <v>118939</v>
       </c>
-      <c r="D223" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="E223" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="F223" s="9">
+      <c r="D254" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="E254" s="9"/>
+      <c r="F254" s="13">
         <v>3.59</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="72" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="70" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
-    <oddHeader>&amp;LBLACK FRIDAY - 26-11-2025&amp;C&amp;P - &amp;N</oddHeader>
+    <oddHeader>&amp;LGIRO DA PRAÇA - 27-11-25 - 21:57&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>
 </worksheet>
 </file>